--- a/data/proyectos.xlsx
+++ b/data/proyectos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gobantioquia-my.sharepoint.com/personal/vtobonl_antioquia_gov_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFF7219A-15B1-4DA2-958D-934E61186574}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{EB6AA456-4B84-40A1-9B64-E05026C77CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F89D261-B712-437F-9D9B-4E53DD984718}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4719" uniqueCount="1072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4720" uniqueCount="1073">
   <si>
     <t>PROYECTOS SIF</t>
   </si>
@@ -4018,6 +4018,9 @@
   <si>
     <t xml:space="preserve">Actividades preliminares 
 Topografía, Exploración geotécnica,y Limpieza de obras transversales </t>
+  </si>
+  <si>
+    <t>25IA111B2394</t>
   </si>
 </sst>
 </file>
@@ -4522,49 +4525,25 @@
     <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4579,14 +4558,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4919,9 +4922,9 @@
   <cols>
     <col min="1" max="1" width="7.33203125" style="33" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="22.33203125" style="33" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" style="33" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5546875" style="33" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="25.44140625" style="55" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="33" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" style="33" customWidth="1"/>
+    <col min="5" max="5" width="25.44140625" style="55" customWidth="1"/>
     <col min="6" max="6" width="49.109375" style="33" customWidth="1"/>
     <col min="7" max="7" width="48.33203125" style="33" customWidth="1"/>
     <col min="8" max="8" width="35.5546875" style="33" hidden="1" customWidth="1"/>
@@ -4944,10 +4947,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="13.8" hidden="1">
-      <c r="B1" s="105" t="s">
+      <c r="B1" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="105"/>
+      <c r="C1" s="107"/>
       <c r="D1" s="78"/>
       <c r="E1" s="34"/>
       <c r="F1" s="78"/>
@@ -5032,7 +5035,7 @@
       <c r="W2" s="13"/>
     </row>
     <row r="3" spans="1:23" ht="62.4" hidden="1" customHeight="1">
-      <c r="A3" s="102">
+      <c r="A3" s="94">
         <v>1</v>
       </c>
       <c r="B3" s="66" t="s">
@@ -5098,7 +5101,7 @@
       </c>
     </row>
     <row r="4" spans="1:23" ht="62.4" hidden="1" customHeight="1">
-      <c r="A4" s="102"/>
+      <c r="A4" s="94"/>
       <c r="B4" s="71" t="s">
         <v>21</v>
       </c>
@@ -5162,7 +5165,7 @@
       </c>
     </row>
     <row r="5" spans="1:23" ht="41.4" hidden="1">
-      <c r="A5" s="102"/>
+      <c r="A5" s="94"/>
       <c r="B5" s="66" t="s">
         <v>21</v>
       </c>
@@ -5270,7 +5273,7 @@
       <c r="U6" s="66"/>
     </row>
     <row r="7" spans="1:23" ht="13.8" hidden="1">
-      <c r="A7" s="101">
+      <c r="A7" s="98">
         <v>2</v>
       </c>
       <c r="B7" s="71" t="s">
@@ -5305,7 +5308,7 @@
       <c r="U7" s="66"/>
     </row>
     <row r="8" spans="1:23" ht="13.8" hidden="1">
-      <c r="A8" s="106"/>
+      <c r="A8" s="93"/>
       <c r="B8" s="71" t="s">
         <v>39</v>
       </c>
@@ -5357,7 +5360,7 @@
       <c r="U8" s="66"/>
     </row>
     <row r="9" spans="1:23" ht="41.4" hidden="1">
-      <c r="A9" s="106"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="71" t="s">
         <v>39</v>
       </c>
@@ -5415,7 +5418,7 @@
       <c r="U9" s="66"/>
     </row>
     <row r="10" spans="1:23" ht="41.4" hidden="1">
-      <c r="A10" s="102"/>
+      <c r="A10" s="94"/>
       <c r="B10" s="66" t="s">
         <v>39</v>
       </c>
@@ -5473,7 +5476,7 @@
       </c>
     </row>
     <row r="11" spans="1:23" ht="27.6" hidden="1">
-      <c r="A11" s="95">
+      <c r="A11" s="92">
         <v>3</v>
       </c>
       <c r="B11" s="71" t="s">
@@ -5536,7 +5539,7 @@
       </c>
     </row>
     <row r="12" spans="1:23" ht="52.95" hidden="1" customHeight="1">
-      <c r="A12" s="95"/>
+      <c r="A12" s="92"/>
       <c r="B12" s="71" t="s">
         <v>57</v>
       </c>
@@ -5592,7 +5595,7 @@
       <c r="U12" s="76"/>
     </row>
     <row r="13" spans="1:23" ht="13.8" hidden="1">
-      <c r="A13" s="95"/>
+      <c r="A13" s="92"/>
       <c r="B13" s="71" t="s">
         <v>57</v>
       </c>
@@ -5648,7 +5651,7 @@
       </c>
     </row>
     <row r="14" spans="1:23" ht="13.8" hidden="1">
-      <c r="A14" s="95"/>
+      <c r="A14" s="92"/>
       <c r="B14" s="71" t="s">
         <v>57</v>
       </c>
@@ -5704,7 +5707,7 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="13.8" hidden="1">
-      <c r="A15" s="95"/>
+      <c r="A15" s="92"/>
       <c r="B15" s="71" t="s">
         <v>57</v>
       </c>
@@ -5760,7 +5763,7 @@
       <c r="U15" s="66"/>
     </row>
     <row r="16" spans="1:23" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A16" s="95"/>
+      <c r="A16" s="92"/>
       <c r="B16" s="71" t="s">
         <v>57</v>
       </c>
@@ -5977,7 +5980,7 @@
       </c>
     </row>
     <row r="20" spans="1:21" ht="97.95" hidden="1" customHeight="1">
-      <c r="A20" s="95">
+      <c r="A20" s="92">
         <v>5</v>
       </c>
       <c r="B20" s="71" t="s">
@@ -6039,7 +6042,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A21" s="95"/>
+      <c r="A21" s="92"/>
       <c r="B21" s="71" t="s">
         <v>90</v>
       </c>
@@ -6097,7 +6100,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" hidden="1">
-      <c r="A22" s="95"/>
+      <c r="A22" s="92"/>
       <c r="B22" s="71"/>
       <c r="C22" s="66" t="s">
         <v>91</v>
@@ -6154,7 +6157,7 @@
       </c>
     </row>
     <row r="23" spans="1:21" ht="13.8" hidden="1">
-      <c r="A23" s="95"/>
+      <c r="A23" s="92"/>
       <c r="B23" s="71" t="s">
         <v>90</v>
       </c>
@@ -6211,7 +6214,7 @@
       <c r="U23" s="71"/>
     </row>
     <row r="24" spans="1:21" ht="66" hidden="1" customHeight="1">
-      <c r="A24" s="95">
+      <c r="A24" s="92">
         <v>6</v>
       </c>
       <c r="B24" s="71" t="s">
@@ -6272,7 +6275,7 @@
       </c>
     </row>
     <row r="25" spans="1:21" ht="13.8" hidden="1">
-      <c r="A25" s="95"/>
+      <c r="A25" s="92"/>
       <c r="B25" s="71" t="s">
         <v>107</v>
       </c>
@@ -6328,7 +6331,7 @@
       </c>
     </row>
     <row r="26" spans="1:21" ht="70.2" hidden="1" customHeight="1">
-      <c r="A26" s="95"/>
+      <c r="A26" s="92"/>
       <c r="B26" s="71" t="s">
         <v>107</v>
       </c>
@@ -6384,7 +6387,7 @@
       </c>
     </row>
     <row r="27" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A27" s="95"/>
+      <c r="A27" s="92"/>
       <c r="B27" s="71" t="s">
         <v>107</v>
       </c>
@@ -6442,7 +6445,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="13.8" hidden="1">
-      <c r="A28" s="95"/>
+      <c r="A28" s="92"/>
       <c r="B28" s="71" t="s">
         <v>107</v>
       </c>
@@ -6496,7 +6499,7 @@
       </c>
     </row>
     <row r="29" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A29" s="95"/>
+      <c r="A29" s="92"/>
       <c r="B29" s="71" t="s">
         <v>107</v>
       </c>
@@ -6552,7 +6555,7 @@
       </c>
     </row>
     <row r="30" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A30" s="95"/>
+      <c r="A30" s="92"/>
       <c r="B30" s="71" t="s">
         <v>107</v>
       </c>
@@ -6604,7 +6607,7 @@
       </c>
     </row>
     <row r="31" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A31" s="95"/>
+      <c r="A31" s="92"/>
       <c r="B31" s="71" t="s">
         <v>107</v>
       </c>
@@ -6662,7 +6665,7 @@
       </c>
     </row>
     <row r="32" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A32" s="95"/>
+      <c r="A32" s="92"/>
       <c r="B32" s="71" t="s">
         <v>107</v>
       </c>
@@ -6722,7 +6725,7 @@
       </c>
     </row>
     <row r="33" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A33" s="95"/>
+      <c r="A33" s="92"/>
       <c r="B33" s="71" t="s">
         <v>107</v>
       </c>
@@ -6778,7 +6781,7 @@
       </c>
     </row>
     <row r="34" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A34" s="95"/>
+      <c r="A34" s="92"/>
       <c r="B34" s="71" t="s">
         <v>107</v>
       </c>
@@ -6838,7 +6841,7 @@
       </c>
     </row>
     <row r="35" spans="1:21" ht="13.8" hidden="1">
-      <c r="A35" s="106"/>
+      <c r="A35" s="93"/>
       <c r="B35" s="71" t="s">
         <v>145</v>
       </c>
@@ -6873,7 +6876,7 @@
       <c r="U35" s="71"/>
     </row>
     <row r="36" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A36" s="102"/>
+      <c r="A36" s="94"/>
       <c r="B36" s="71" t="s">
         <v>145</v>
       </c>
@@ -6985,7 +6988,7 @@
       </c>
     </row>
     <row r="38" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A38" s="95">
+      <c r="A38" s="92">
         <v>8</v>
       </c>
       <c r="B38" s="71" t="s">
@@ -7046,7 +7049,7 @@
       </c>
     </row>
     <row r="39" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A39" s="95"/>
+      <c r="A39" s="92"/>
       <c r="B39" s="71" t="s">
         <v>148</v>
       </c>
@@ -7106,7 +7109,7 @@
       </c>
     </row>
     <row r="40" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A40" s="95"/>
+      <c r="A40" s="92"/>
       <c r="B40" s="71" t="s">
         <v>148</v>
       </c>
@@ -7163,7 +7166,7 @@
       </c>
     </row>
     <row r="41" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A41" s="95">
+      <c r="A41" s="92">
         <v>9</v>
       </c>
       <c r="B41" s="71" t="s">
@@ -7223,7 +7226,7 @@
       <c r="U41" s="71"/>
     </row>
     <row r="42" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A42" s="95"/>
+      <c r="A42" s="92"/>
       <c r="B42" s="71" t="s">
         <v>158</v>
       </c>
@@ -7272,7 +7275,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A43" s="95"/>
+      <c r="A43" s="92"/>
       <c r="B43" s="71" t="s">
         <v>158</v>
       </c>
@@ -7323,7 +7326,7 @@
       </c>
     </row>
     <row r="44" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A44" s="95"/>
+      <c r="A44" s="92"/>
       <c r="B44" s="71" t="s">
         <v>158</v>
       </c>
@@ -7371,7 +7374,7 @@
       </c>
     </row>
     <row r="45" spans="1:21" ht="27.6" hidden="1">
-      <c r="A45" s="95"/>
+      <c r="A45" s="92"/>
       <c r="B45" s="71" t="s">
         <v>158</v>
       </c>
@@ -7427,7 +7430,7 @@
       </c>
     </row>
     <row r="46" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A46" s="95">
+      <c r="A46" s="92">
         <v>10</v>
       </c>
       <c r="B46" s="71" t="s">
@@ -7483,7 +7486,7 @@
       </c>
     </row>
     <row r="47" spans="1:21" ht="13.8" hidden="1">
-      <c r="A47" s="101"/>
+      <c r="A47" s="98"/>
       <c r="B47" s="71" t="s">
         <v>173</v>
       </c>
@@ -7537,7 +7540,7 @@
       <c r="U47" s="71"/>
     </row>
     <row r="48" spans="1:21" ht="13.8" hidden="1">
-      <c r="A48" s="95"/>
+      <c r="A48" s="92"/>
       <c r="B48" s="71" t="s">
         <v>180</v>
       </c>
@@ -7572,7 +7575,7 @@
       <c r="U48" s="71"/>
     </row>
     <row r="49" spans="1:21" ht="13.8" hidden="1">
-      <c r="A49" s="95"/>
+      <c r="A49" s="92"/>
       <c r="B49" s="71" t="s">
         <v>180</v>
       </c>
@@ -7611,7 +7614,7 @@
       </c>
     </row>
     <row r="50" spans="1:21" ht="13.8" hidden="1">
-      <c r="A50" s="95"/>
+      <c r="A50" s="92"/>
       <c r="B50" s="71" t="s">
         <v>180</v>
       </c>
@@ -7665,7 +7668,7 @@
       </c>
     </row>
     <row r="51" spans="1:21" ht="55.2" hidden="1">
-      <c r="A51" s="95"/>
+      <c r="A51" s="92"/>
       <c r="B51" s="71" t="s">
         <v>180</v>
       </c>
@@ -7719,7 +7722,7 @@
       </c>
     </row>
     <row r="52" spans="1:21" ht="41.4" hidden="1">
-      <c r="A52" s="95"/>
+      <c r="A52" s="92"/>
       <c r="B52" s="71" t="s">
         <v>180</v>
       </c>
@@ -7773,7 +7776,7 @@
       </c>
     </row>
     <row r="53" spans="1:21" ht="45.6" hidden="1" customHeight="1">
-      <c r="A53" s="95"/>
+      <c r="A53" s="92"/>
       <c r="B53" s="71" t="s">
         <v>180</v>
       </c>
@@ -7827,7 +7830,7 @@
       </c>
     </row>
     <row r="54" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A54" s="95"/>
+      <c r="A54" s="92"/>
       <c r="B54" s="71" t="s">
         <v>195</v>
       </c>
@@ -7880,7 +7883,7 @@
       </c>
     </row>
     <row r="55" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A55" s="95"/>
+      <c r="A55" s="92"/>
       <c r="B55" s="71" t="s">
         <v>195</v>
       </c>
@@ -7934,7 +7937,7 @@
       <c r="U55" s="66"/>
     </row>
     <row r="56" spans="1:21" ht="41.4" hidden="1">
-      <c r="A56" s="95"/>
+      <c r="A56" s="92"/>
       <c r="B56" s="71" t="s">
         <v>195</v>
       </c>
@@ -7992,7 +7995,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A57" s="95"/>
+      <c r="A57" s="92"/>
       <c r="B57" s="71" t="s">
         <v>195</v>
       </c>
@@ -8048,7 +8051,7 @@
       <c r="U57" s="71"/>
     </row>
     <row r="58" spans="1:21" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A58" s="95"/>
+      <c r="A58" s="92"/>
       <c r="B58" s="71" t="s">
         <v>195</v>
       </c>
@@ -8107,7 +8110,7 @@
       </c>
     </row>
     <row r="59" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A59" s="102"/>
+      <c r="A59" s="94"/>
       <c r="B59" s="71" t="s">
         <v>207</v>
       </c>
@@ -8163,7 +8166,7 @@
       </c>
     </row>
     <row r="60" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A60" s="102"/>
+      <c r="A60" s="94"/>
       <c r="B60" s="71" t="s">
         <v>207</v>
       </c>
@@ -8218,7 +8221,7 @@
       </c>
     </row>
     <row r="61" spans="1:21" ht="41.4" hidden="1">
-      <c r="A61" s="95"/>
+      <c r="A61" s="92"/>
       <c r="B61" s="61" t="s">
         <v>207</v>
       </c>
@@ -8271,7 +8274,7 @@
       </c>
     </row>
     <row r="62" spans="1:21" ht="33" hidden="1" customHeight="1">
-      <c r="A62" s="101">
+      <c r="A62" s="98">
         <v>14</v>
       </c>
       <c r="B62" s="71" t="s">
@@ -8328,7 +8331,7 @@
       </c>
     </row>
     <row r="63" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A63" s="106"/>
+      <c r="A63" s="93"/>
       <c r="B63" s="71" t="s">
         <v>213</v>
       </c>
@@ -8384,7 +8387,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="107.25" hidden="1" customHeight="1">
-      <c r="A64" s="102"/>
+      <c r="A64" s="94"/>
       <c r="B64" s="71" t="s">
         <v>213</v>
       </c>
@@ -8546,7 +8549,7 @@
       </c>
     </row>
     <row r="67" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A67" s="101">
+      <c r="A67" s="98">
         <v>16</v>
       </c>
       <c r="B67" s="71" t="s">
@@ -8601,7 +8604,7 @@
       </c>
     </row>
     <row r="68" spans="1:21" ht="13.8" hidden="1">
-      <c r="A68" s="102"/>
+      <c r="A68" s="94"/>
       <c r="B68" s="71" t="s">
         <v>228</v>
       </c>
@@ -8653,7 +8656,7 @@
       </c>
     </row>
     <row r="69" spans="1:21" ht="51.6" hidden="1" customHeight="1">
-      <c r="A69" s="101">
+      <c r="A69" s="98">
         <v>17</v>
       </c>
       <c r="B69" s="71" t="s">
@@ -8708,7 +8711,7 @@
       </c>
     </row>
     <row r="70" spans="1:21" ht="41.4" hidden="1">
-      <c r="A70" s="106"/>
+      <c r="A70" s="93"/>
       <c r="B70" s="71" t="s">
         <v>234</v>
       </c>
@@ -8762,7 +8765,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="67.95" hidden="1" customHeight="1">
-      <c r="A71" s="106"/>
+      <c r="A71" s="93"/>
       <c r="B71" s="71" t="s">
         <v>240</v>
       </c>
@@ -8816,7 +8819,7 @@
       </c>
     </row>
     <row r="72" spans="1:21" ht="174.6" hidden="1" customHeight="1">
-      <c r="A72" s="106"/>
+      <c r="A72" s="93"/>
       <c r="B72" s="71" t="s">
         <v>243</v>
       </c>
@@ -8871,7 +8874,7 @@
       </c>
     </row>
     <row r="73" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A73" s="106"/>
+      <c r="A73" s="93"/>
       <c r="B73" s="71" t="s">
         <v>243</v>
       </c>
@@ -8923,7 +8926,7 @@
       </c>
     </row>
     <row r="74" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A74" s="106"/>
+      <c r="A74" s="93"/>
       <c r="B74" s="71" t="s">
         <v>243</v>
       </c>
@@ -8977,7 +8980,7 @@
       </c>
     </row>
     <row r="75" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A75" s="106"/>
+      <c r="A75" s="93"/>
       <c r="B75" s="71" t="s">
         <v>243</v>
       </c>
@@ -9037,7 +9040,7 @@
       </c>
     </row>
     <row r="76" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A76" s="106"/>
+      <c r="A76" s="93"/>
       <c r="B76" s="71" t="s">
         <v>243</v>
       </c>
@@ -9089,7 +9092,7 @@
       <c r="U76" s="71"/>
     </row>
     <row r="77" spans="1:21" ht="13.8" hidden="1">
-      <c r="A77" s="102"/>
+      <c r="A77" s="94"/>
       <c r="B77" s="71" t="s">
         <v>243</v>
       </c>
@@ -9145,7 +9148,7 @@
       </c>
     </row>
     <row r="78" spans="1:21" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A78" s="106"/>
+      <c r="A78" s="93"/>
       <c r="B78" s="71" t="s">
         <v>254</v>
       </c>
@@ -9205,7 +9208,7 @@
       </c>
     </row>
     <row r="79" spans="1:21" ht="13.8" hidden="1">
-      <c r="A79" s="106"/>
+      <c r="A79" s="93"/>
       <c r="B79" s="71" t="s">
         <v>254</v>
       </c>
@@ -9259,7 +9262,7 @@
       <c r="U79" s="66"/>
     </row>
     <row r="80" spans="1:21" ht="13.8" hidden="1">
-      <c r="A80" s="106"/>
+      <c r="A80" s="93"/>
       <c r="B80" s="71" t="s">
         <v>254</v>
       </c>
@@ -9313,7 +9316,7 @@
       <c r="U80" s="66"/>
     </row>
     <row r="81" spans="1:22" ht="150.6" hidden="1" customHeight="1">
-      <c r="A81" s="106"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="71" t="s">
         <v>254</v>
       </c>
@@ -9368,7 +9371,7 @@
       </c>
     </row>
     <row r="82" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A82" s="106"/>
+      <c r="A82" s="93"/>
       <c r="B82" s="71" t="s">
         <v>263</v>
       </c>
@@ -9425,7 +9428,7 @@
       <c r="V82" s="33"/>
     </row>
     <row r="83" spans="1:22" ht="38.4" hidden="1" customHeight="1">
-      <c r="A83" s="106"/>
+      <c r="A83" s="93"/>
       <c r="B83" s="71" t="s">
         <v>263</v>
       </c>
@@ -9479,7 +9482,7 @@
       <c r="V83" s="33"/>
     </row>
     <row r="84" spans="1:22" ht="27.6" hidden="1">
-      <c r="A84" s="106"/>
+      <c r="A84" s="93"/>
       <c r="B84" s="71" t="s">
         <v>263</v>
       </c>
@@ -9533,7 +9536,7 @@
       </c>
     </row>
     <row r="85" spans="1:22" ht="55.2" hidden="1">
-      <c r="A85" s="106"/>
+      <c r="A85" s="93"/>
       <c r="B85" s="71" t="s">
         <v>263</v>
       </c>
@@ -9586,7 +9589,7 @@
       <c r="V85" s="33"/>
     </row>
     <row r="86" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A86" s="106"/>
+      <c r="A86" s="93"/>
       <c r="B86" s="71" t="s">
         <v>263</v>
       </c>
@@ -9643,7 +9646,7 @@
       <c r="V86" s="33"/>
     </row>
     <row r="87" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A87" s="106"/>
+      <c r="A87" s="93"/>
       <c r="B87" s="71" t="s">
         <v>263</v>
       </c>
@@ -9700,7 +9703,7 @@
       <c r="V87" s="33"/>
     </row>
     <row r="88" spans="1:22" ht="13.8" hidden="1">
-      <c r="A88" s="106"/>
+      <c r="A88" s="93"/>
       <c r="B88" s="71" t="s">
         <v>263</v>
       </c>
@@ -9757,7 +9760,7 @@
       <c r="V88" s="33"/>
     </row>
     <row r="89" spans="1:22" ht="13.8" hidden="1">
-      <c r="A89" s="106"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="71" t="s">
         <v>263</v>
       </c>
@@ -9812,7 +9815,7 @@
       <c r="V89" s="33"/>
     </row>
     <row r="90" spans="1:22" ht="18" hidden="1" customHeight="1">
-      <c r="A90" s="106"/>
+      <c r="A90" s="93"/>
       <c r="B90" s="66" t="s">
         <v>263</v>
       </c>
@@ -9861,7 +9864,7 @@
       <c r="V90" s="33"/>
     </row>
     <row r="91" spans="1:22" ht="43.95" hidden="1" customHeight="1">
-      <c r="A91" s="106"/>
+      <c r="A91" s="93"/>
       <c r="B91" s="71" t="s">
         <v>283</v>
       </c>
@@ -9885,35 +9888,35 @@
       </c>
       <c r="I91" s="71"/>
       <c r="J91" s="71"/>
-      <c r="K91" s="92"/>
-      <c r="L91" s="92">
+      <c r="K91" s="108"/>
+      <c r="L91" s="108">
         <v>0</v>
       </c>
-      <c r="M91" s="92"/>
-      <c r="N91" s="95" t="s">
+      <c r="M91" s="108"/>
+      <c r="N91" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="O91" s="95" t="s">
+      <c r="O91" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="P91" s="95">
+      <c r="P91" s="92">
         <v>2026</v>
       </c>
-      <c r="Q91" s="96" t="s">
+      <c r="Q91" s="97" t="s">
         <v>129</v>
       </c>
       <c r="R91" s="71"/>
       <c r="S91" s="71"/>
-      <c r="T91" s="97">
+      <c r="T91" s="111">
         <v>0</v>
       </c>
-      <c r="U91" s="96" t="s">
+      <c r="U91" s="97" t="s">
         <v>286</v>
       </c>
       <c r="V91" s="33"/>
     </row>
     <row r="92" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A92" s="106"/>
+      <c r="A92" s="93"/>
       <c r="B92" s="71" t="s">
         <v>283</v>
       </c>
@@ -9937,20 +9940,20 @@
       </c>
       <c r="I92" s="71"/>
       <c r="J92" s="71"/>
-      <c r="K92" s="93"/>
-      <c r="L92" s="93"/>
-      <c r="M92" s="93"/>
-      <c r="N92" s="95"/>
-      <c r="O92" s="95"/>
-      <c r="P92" s="95"/>
-      <c r="Q92" s="96"/>
+      <c r="K92" s="109"/>
+      <c r="L92" s="109"/>
+      <c r="M92" s="109"/>
+      <c r="N92" s="92"/>
+      <c r="O92" s="92"/>
+      <c r="P92" s="92"/>
+      <c r="Q92" s="97"/>
       <c r="R92" s="71"/>
       <c r="S92" s="71"/>
-      <c r="T92" s="97"/>
-      <c r="U92" s="96"/>
+      <c r="T92" s="111"/>
+      <c r="U92" s="97"/>
     </row>
     <row r="93" spans="1:22" ht="18" hidden="1" customHeight="1">
-      <c r="A93" s="106"/>
+      <c r="A93" s="93"/>
       <c r="B93" s="71" t="s">
         <v>283</v>
       </c>
@@ -9974,9 +9977,9 @@
       </c>
       <c r="I93" s="71"/>
       <c r="J93" s="71"/>
-      <c r="K93" s="93"/>
-      <c r="L93" s="93"/>
-      <c r="M93" s="93"/>
+      <c r="K93" s="109"/>
+      <c r="L93" s="109"/>
+      <c r="M93" s="109"/>
       <c r="N93" s="66" t="s">
         <v>28</v>
       </c>
@@ -9999,7 +10002,7 @@
       </c>
     </row>
     <row r="94" spans="1:22" ht="18" hidden="1" customHeight="1">
-      <c r="A94" s="106"/>
+      <c r="A94" s="93"/>
       <c r="B94" s="71" t="s">
         <v>283</v>
       </c>
@@ -10021,9 +10024,9 @@
       </c>
       <c r="I94" s="71"/>
       <c r="J94" s="71"/>
-      <c r="K94" s="93"/>
-      <c r="L94" s="93"/>
-      <c r="M94" s="93"/>
+      <c r="K94" s="109"/>
+      <c r="L94" s="109"/>
+      <c r="M94" s="109"/>
       <c r="N94" s="66" t="s">
         <v>28</v>
       </c>
@@ -10046,7 +10049,7 @@
       </c>
     </row>
     <row r="95" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A95" s="106"/>
+      <c r="A95" s="93"/>
       <c r="B95" s="71" t="s">
         <v>283</v>
       </c>
@@ -10070,9 +10073,9 @@
       </c>
       <c r="I95" s="66"/>
       <c r="J95" s="66"/>
-      <c r="K95" s="93"/>
-      <c r="L95" s="93"/>
-      <c r="M95" s="93"/>
+      <c r="K95" s="109"/>
+      <c r="L95" s="109"/>
+      <c r="M95" s="109"/>
       <c r="N95" s="66" t="s">
         <v>147</v>
       </c>
@@ -10095,7 +10098,7 @@
       </c>
     </row>
     <row r="96" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A96" s="106"/>
+      <c r="A96" s="93"/>
       <c r="B96" s="71" t="s">
         <v>291</v>
       </c>
@@ -10115,9 +10118,9 @@
       <c r="H96" s="66"/>
       <c r="I96" s="66"/>
       <c r="J96" s="66"/>
-      <c r="K96" s="93"/>
-      <c r="L96" s="93"/>
-      <c r="M96" s="93"/>
+      <c r="K96" s="109"/>
+      <c r="L96" s="109"/>
+      <c r="M96" s="109"/>
       <c r="N96" s="66"/>
       <c r="O96" s="66"/>
       <c r="P96" s="66"/>
@@ -10128,7 +10131,7 @@
       <c r="U96" s="66"/>
     </row>
     <row r="97" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A97" s="106"/>
+      <c r="A97" s="93"/>
       <c r="B97" s="71" t="s">
         <v>291</v>
       </c>
@@ -10156,9 +10159,9 @@
       <c r="J97" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="K97" s="93"/>
-      <c r="L97" s="93"/>
-      <c r="M97" s="93"/>
+      <c r="K97" s="109"/>
+      <c r="L97" s="109"/>
+      <c r="M97" s="109"/>
       <c r="N97" s="66" t="s">
         <v>28</v>
       </c>
@@ -10179,7 +10182,7 @@
       </c>
     </row>
     <row r="98" spans="1:21" ht="99.6" hidden="1" customHeight="1">
-      <c r="A98" s="106"/>
+      <c r="A98" s="93"/>
       <c r="B98" s="71" t="s">
         <v>291</v>
       </c>
@@ -10207,9 +10210,9 @@
       <c r="J98" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="K98" s="93"/>
-      <c r="L98" s="93"/>
-      <c r="M98" s="93"/>
+      <c r="K98" s="109"/>
+      <c r="L98" s="109"/>
+      <c r="M98" s="109"/>
       <c r="N98" s="66" t="s">
         <v>99</v>
       </c>
@@ -10232,7 +10235,7 @@
       </c>
     </row>
     <row r="99" spans="1:21" ht="17.399999999999999" hidden="1" customHeight="1">
-      <c r="A99" s="106"/>
+      <c r="A99" s="93"/>
       <c r="B99" s="71" t="s">
         <v>300</v>
       </c>
@@ -10256,9 +10259,9 @@
       </c>
       <c r="I99" s="66"/>
       <c r="J99" s="66"/>
-      <c r="K99" s="93"/>
-      <c r="L99" s="93"/>
-      <c r="M99" s="93"/>
+      <c r="K99" s="109"/>
+      <c r="L99" s="109"/>
+      <c r="M99" s="109"/>
       <c r="N99" s="66" t="s">
         <v>147</v>
       </c>
@@ -10281,7 +10284,7 @@
       </c>
     </row>
     <row r="100" spans="1:21" ht="17.399999999999999" hidden="1" customHeight="1">
-      <c r="A100" s="106"/>
+      <c r="A100" s="93"/>
       <c r="B100" s="71" t="s">
         <v>300</v>
       </c>
@@ -10305,9 +10308,9 @@
       </c>
       <c r="I100" s="66"/>
       <c r="J100" s="66"/>
-      <c r="K100" s="93"/>
-      <c r="L100" s="93"/>
-      <c r="M100" s="93"/>
+      <c r="K100" s="109"/>
+      <c r="L100" s="109"/>
+      <c r="M100" s="109"/>
       <c r="N100" s="66" t="s">
         <v>73</v>
       </c>
@@ -10330,7 +10333,7 @@
       </c>
     </row>
     <row r="101" spans="1:21" ht="53.4" hidden="1" customHeight="1">
-      <c r="A101" s="106"/>
+      <c r="A101" s="93"/>
       <c r="B101" s="71" t="s">
         <v>300</v>
       </c>
@@ -10354,9 +10357,9 @@
       </c>
       <c r="I101" s="71"/>
       <c r="J101" s="71"/>
-      <c r="K101" s="94"/>
-      <c r="L101" s="94"/>
-      <c r="M101" s="94"/>
+      <c r="K101" s="110"/>
+      <c r="L101" s="110"/>
+      <c r="M101" s="110"/>
       <c r="N101" s="66" t="s">
         <v>36</v>
       </c>
@@ -10379,7 +10382,7 @@
       </c>
     </row>
     <row r="102" spans="1:21" ht="53.4" hidden="1" customHeight="1">
-      <c r="A102" s="106"/>
+      <c r="A102" s="93"/>
       <c r="B102" s="71" t="s">
         <v>300</v>
       </c>
@@ -10435,7 +10438,7 @@
       </c>
     </row>
     <row r="103" spans="1:21" ht="53.4" hidden="1" customHeight="1">
-      <c r="A103" s="106"/>
+      <c r="A103" s="93"/>
       <c r="B103" s="71" t="s">
         <v>300</v>
       </c>
@@ -10486,7 +10489,7 @@
       </c>
     </row>
     <row r="104" spans="1:21" ht="53.4" hidden="1" customHeight="1">
-      <c r="A104" s="106"/>
+      <c r="A104" s="93"/>
       <c r="B104" s="71" t="s">
         <v>300</v>
       </c>
@@ -10538,7 +10541,7 @@
       </c>
     </row>
     <row r="105" spans="1:21" ht="53.4" hidden="1" customHeight="1">
-      <c r="A105" s="106"/>
+      <c r="A105" s="93"/>
       <c r="B105" s="71" t="s">
         <v>300</v>
       </c>
@@ -10592,7 +10595,7 @@
       <c r="U105" s="66"/>
     </row>
     <row r="106" spans="1:21" ht="34.5" hidden="1" customHeight="1">
-      <c r="A106" s="106"/>
+      <c r="A106" s="93"/>
       <c r="B106" s="71" t="s">
         <v>300</v>
       </c>
@@ -10646,7 +10649,7 @@
       </c>
     </row>
     <row r="107" spans="1:21" ht="96.6" hidden="1">
-      <c r="A107" s="106"/>
+      <c r="A107" s="93"/>
       <c r="B107" s="71" t="s">
         <v>312</v>
       </c>
@@ -10697,7 +10700,7 @@
       </c>
     </row>
     <row r="108" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A108" s="106"/>
+      <c r="A108" s="93"/>
       <c r="B108" s="71" t="s">
         <v>318</v>
       </c>
@@ -10742,7 +10745,7 @@
       </c>
     </row>
     <row r="109" spans="1:21" ht="13.8" hidden="1">
-      <c r="A109" s="106"/>
+      <c r="A109" s="93"/>
       <c r="B109" s="71" t="s">
         <v>318</v>
       </c>
@@ -10794,7 +10797,7 @@
       <c r="U109" s="66"/>
     </row>
     <row r="110" spans="1:21" ht="13.8" hidden="1">
-      <c r="A110" s="106"/>
+      <c r="A110" s="93"/>
       <c r="B110" s="71" t="s">
         <v>318</v>
       </c>
@@ -10848,7 +10851,7 @@
       <c r="U110" s="71"/>
     </row>
     <row r="111" spans="1:21" ht="60.6" hidden="1" customHeight="1">
-      <c r="A111" s="106"/>
+      <c r="A111" s="93"/>
       <c r="B111" s="71" t="s">
         <v>323</v>
       </c>
@@ -10906,7 +10909,7 @@
       <c r="U111" s="71"/>
     </row>
     <row r="112" spans="1:21" ht="13.8" hidden="1">
-      <c r="A112" s="106"/>
+      <c r="A112" s="93"/>
       <c r="B112" s="71" t="s">
         <v>325</v>
       </c>
@@ -10958,7 +10961,7 @@
       </c>
     </row>
     <row r="113" spans="1:21" ht="13.8" hidden="1">
-      <c r="A113" s="106"/>
+      <c r="A113" s="93"/>
       <c r="B113" s="71" t="s">
         <v>325</v>
       </c>
@@ -11010,7 +11013,7 @@
       </c>
     </row>
     <row r="114" spans="1:21" ht="41.4" hidden="1">
-      <c r="A114" s="106"/>
+      <c r="A114" s="93"/>
       <c r="B114" s="71" t="s">
         <v>325</v>
       </c>
@@ -11051,7 +11054,7 @@
       </c>
     </row>
     <row r="115" spans="1:21" ht="22.95" hidden="1" customHeight="1">
-      <c r="A115" s="106"/>
+      <c r="A115" s="93"/>
       <c r="B115" s="71" t="s">
         <v>325</v>
       </c>
@@ -11107,7 +11110,7 @@
       </c>
     </row>
     <row r="116" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A116" s="106"/>
+      <c r="A116" s="93"/>
       <c r="B116" s="71" t="s">
         <v>335</v>
       </c>
@@ -11167,7 +11170,7 @@
       </c>
     </row>
     <row r="117" spans="1:21" ht="55.2" hidden="1">
-      <c r="A117" s="102"/>
+      <c r="A117" s="94"/>
       <c r="B117" s="71" t="s">
         <v>340</v>
       </c>
@@ -11279,7 +11282,7 @@
       <c r="U118" s="71"/>
     </row>
     <row r="119" spans="1:21" ht="39.6" hidden="1" customHeight="1">
-      <c r="A119" s="95">
+      <c r="A119" s="92">
         <v>30</v>
       </c>
       <c r="B119" s="71" t="s">
@@ -11333,7 +11336,7 @@
       <c r="U119" s="71"/>
     </row>
     <row r="120" spans="1:21" ht="13.8" hidden="1">
-      <c r="A120" s="95"/>
+      <c r="A120" s="92"/>
       <c r="B120" s="71" t="s">
         <v>345</v>
       </c>
@@ -11387,7 +11390,7 @@
       <c r="U120" s="66"/>
     </row>
     <row r="121" spans="1:21" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A121" s="111">
+      <c r="A121" s="106">
         <v>31</v>
       </c>
       <c r="B121" s="71" t="s">
@@ -11442,7 +11445,7 @@
       </c>
     </row>
     <row r="122" spans="1:21" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A122" s="96"/>
+      <c r="A122" s="97"/>
       <c r="B122" s="71" t="s">
         <v>348</v>
       </c>
@@ -11495,7 +11498,7 @@
       </c>
     </row>
     <row r="123" spans="1:21" ht="142.94999999999999" hidden="1" customHeight="1">
-      <c r="A123" s="96"/>
+      <c r="A123" s="97"/>
       <c r="B123" s="71" t="s">
         <v>348</v>
       </c>
@@ -11549,7 +11552,7 @@
       </c>
     </row>
     <row r="124" spans="1:21" ht="13.8" hidden="1">
-      <c r="A124" s="96"/>
+      <c r="A124" s="97"/>
       <c r="B124" s="71" t="s">
         <v>348</v>
       </c>
@@ -12036,7 +12039,7 @@
       <c r="U132" s="66"/>
     </row>
     <row r="133" spans="1:21" ht="13.8" hidden="1">
-      <c r="A133" s="95">
+      <c r="A133" s="92">
         <v>35</v>
       </c>
       <c r="B133" s="71" t="s">
@@ -12094,7 +12097,7 @@
       </c>
     </row>
     <row r="134" spans="1:21" ht="13.8" hidden="1">
-      <c r="A134" s="95"/>
+      <c r="A134" s="92"/>
       <c r="B134" s="71" t="s">
         <v>372</v>
       </c>
@@ -12148,7 +12151,7 @@
       <c r="U134" s="66"/>
     </row>
     <row r="135" spans="1:21" ht="41.4" hidden="1">
-      <c r="A135" s="95"/>
+      <c r="A135" s="92"/>
       <c r="B135" s="71" t="s">
         <v>372</v>
       </c>
@@ -12208,7 +12211,7 @@
       </c>
     </row>
     <row r="136" spans="1:21" ht="13.8" hidden="1">
-      <c r="A136" s="95"/>
+      <c r="A136" s="92"/>
       <c r="B136" s="71" t="s">
         <v>372</v>
       </c>
@@ -12321,7 +12324,7 @@
       <c r="U137" s="71"/>
     </row>
     <row r="138" spans="1:21" ht="13.8" hidden="1">
-      <c r="A138" s="95">
+      <c r="A138" s="92">
         <v>36</v>
       </c>
       <c r="B138" s="71" t="s">
@@ -12377,7 +12380,7 @@
       <c r="U138" s="71"/>
     </row>
     <row r="139" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A139" s="95"/>
+      <c r="A139" s="92"/>
       <c r="B139" s="71" t="s">
         <v>381</v>
       </c>
@@ -12431,7 +12434,7 @@
       <c r="U139" s="71"/>
     </row>
     <row r="140" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A140" s="95"/>
+      <c r="A140" s="92"/>
       <c r="B140" s="71" t="s">
         <v>381</v>
       </c>
@@ -12485,7 +12488,7 @@
       <c r="U140" s="71"/>
     </row>
     <row r="141" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A141" s="95"/>
+      <c r="A141" s="92"/>
       <c r="B141" s="71" t="s">
         <v>381</v>
       </c>
@@ -12538,7 +12541,7 @@
       <c r="U141" s="71"/>
     </row>
     <row r="142" spans="1:21" ht="13.8" hidden="1">
-      <c r="A142" s="95"/>
+      <c r="A142" s="92"/>
       <c r="B142" s="71" t="s">
         <v>381</v>
       </c>
@@ -12592,7 +12595,7 @@
       <c r="U142" s="71"/>
     </row>
     <row r="143" spans="1:21" ht="13.8" hidden="1">
-      <c r="A143" s="95"/>
+      <c r="A143" s="92"/>
       <c r="B143" s="71" t="s">
         <v>381</v>
       </c>
@@ -12646,7 +12649,7 @@
       <c r="U143" s="66"/>
     </row>
     <row r="144" spans="1:21" ht="13.8" hidden="1">
-      <c r="A144" s="95"/>
+      <c r="A144" s="92"/>
       <c r="B144" s="71" t="s">
         <v>381</v>
       </c>
@@ -12700,7 +12703,7 @@
       <c r="U144" s="71"/>
     </row>
     <row r="145" spans="1:21" ht="13.8" hidden="1">
-      <c r="A145" s="95">
+      <c r="A145" s="92">
         <v>37</v>
       </c>
       <c r="B145" s="71" t="s">
@@ -12758,7 +12761,7 @@
       </c>
     </row>
     <row r="146" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A146" s="95"/>
+      <c r="A146" s="92"/>
       <c r="B146" s="71" t="s">
         <v>397</v>
       </c>
@@ -12810,7 +12813,7 @@
       </c>
     </row>
     <row r="147" spans="1:21" ht="18.600000000000001" hidden="1" customHeight="1">
-      <c r="A147" s="95"/>
+      <c r="A147" s="92"/>
       <c r="B147" s="71" t="s">
         <v>397</v>
       </c>
@@ -12918,7 +12921,7 @@
       </c>
     </row>
     <row r="149" spans="1:21" ht="35.4" hidden="1" customHeight="1">
-      <c r="A149" s="106"/>
+      <c r="A149" s="93"/>
       <c r="B149" s="71" t="s">
         <v>402</v>
       </c>
@@ -12971,7 +12974,7 @@
       </c>
     </row>
     <row r="150" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A150" s="102"/>
+      <c r="A150" s="94"/>
       <c r="B150" s="71" t="s">
         <v>402</v>
       </c>
@@ -13138,7 +13141,7 @@
       </c>
     </row>
     <row r="153" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A153" s="101">
+      <c r="A153" s="98">
         <v>40</v>
       </c>
       <c r="B153" s="71" t="s">
@@ -13196,7 +13199,7 @@
       </c>
     </row>
     <row r="154" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A154" s="106"/>
+      <c r="A154" s="93"/>
       <c r="B154" s="71" t="s">
         <v>413</v>
       </c>
@@ -13247,7 +13250,7 @@
       </c>
     </row>
     <row r="155" spans="1:21" ht="183.6" hidden="1" customHeight="1">
-      <c r="A155" s="106"/>
+      <c r="A155" s="93"/>
       <c r="B155" s="71" t="s">
         <v>413</v>
       </c>
@@ -13296,7 +13299,7 @@
       </c>
     </row>
     <row r="156" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A156" s="106"/>
+      <c r="A156" s="93"/>
       <c r="B156" s="71" t="s">
         <v>413</v>
       </c>
@@ -13347,7 +13350,7 @@
       </c>
     </row>
     <row r="157" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A157" s="106"/>
+      <c r="A157" s="93"/>
       <c r="B157" s="71" t="s">
         <v>413</v>
       </c>
@@ -13403,7 +13406,7 @@
       </c>
     </row>
     <row r="158" spans="1:21" ht="13.8" hidden="1">
-      <c r="A158" s="106"/>
+      <c r="A158" s="93"/>
       <c r="B158" s="71" t="s">
         <v>413</v>
       </c>
@@ -13459,7 +13462,7 @@
       </c>
     </row>
     <row r="159" spans="1:21" ht="13.8" hidden="1">
-      <c r="A159" s="106"/>
+      <c r="A159" s="93"/>
       <c r="B159" s="71" t="s">
         <v>413</v>
       </c>
@@ -13515,7 +13518,7 @@
       </c>
     </row>
     <row r="160" spans="1:21" ht="55.2" hidden="1">
-      <c r="A160" s="106"/>
+      <c r="A160" s="93"/>
       <c r="B160" s="71" t="s">
         <v>427</v>
       </c>
@@ -13567,7 +13570,7 @@
       <c r="U160" s="71"/>
     </row>
     <row r="161" spans="1:21" ht="27.6" hidden="1">
-      <c r="A161" s="106"/>
+      <c r="A161" s="93"/>
       <c r="B161" s="71" t="s">
         <v>427</v>
       </c>
@@ -13622,7 +13625,7 @@
       <c r="U161" s="71"/>
     </row>
     <row r="162" spans="1:21" ht="13.8" hidden="1">
-      <c r="A162" s="106"/>
+      <c r="A162" s="93"/>
       <c r="B162" s="71" t="s">
         <v>427</v>
       </c>
@@ -13674,7 +13677,7 @@
       <c r="U162" s="71"/>
     </row>
     <row r="163" spans="1:21" ht="13.8" hidden="1">
-      <c r="A163" s="106"/>
+      <c r="A163" s="93"/>
       <c r="B163" s="71" t="s">
         <v>427</v>
       </c>
@@ -13730,7 +13733,7 @@
       </c>
     </row>
     <row r="164" spans="1:21" ht="27.75" hidden="1" customHeight="1">
-      <c r="A164" s="102"/>
+      <c r="A164" s="94"/>
       <c r="B164" s="71" t="s">
         <v>435</v>
       </c>
@@ -13783,7 +13786,7 @@
       </c>
     </row>
     <row r="165" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A165" s="106"/>
+      <c r="A165" s="93"/>
       <c r="B165" s="71" t="s">
         <v>435</v>
       </c>
@@ -13836,7 +13839,7 @@
       </c>
     </row>
     <row r="166" spans="1:21" ht="13.8" hidden="1">
-      <c r="A166" s="102"/>
+      <c r="A166" s="94"/>
       <c r="B166" s="71" t="s">
         <v>435</v>
       </c>
@@ -14011,7 +14014,7 @@
       </c>
     </row>
     <row r="169" spans="1:21" ht="41.4" hidden="1">
-      <c r="A169" s="107">
+      <c r="A169" s="99">
         <v>44</v>
       </c>
       <c r="B169" s="71" t="s">
@@ -14071,7 +14074,7 @@
       </c>
     </row>
     <row r="170" spans="1:21" ht="45" hidden="1" customHeight="1">
-      <c r="A170" s="108"/>
+      <c r="A170" s="100"/>
       <c r="B170" s="71" t="s">
         <v>449</v>
       </c>
@@ -14122,7 +14125,7 @@
       </c>
     </row>
     <row r="171" spans="1:21" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A171" s="108"/>
+      <c r="A171" s="100"/>
       <c r="B171" s="71" t="s">
         <v>449</v>
       </c>
@@ -14180,7 +14183,7 @@
       </c>
     </row>
     <row r="172" spans="1:21" ht="13.8" hidden="1">
-      <c r="A172" s="108"/>
+      <c r="A172" s="100"/>
       <c r="B172" s="71" t="s">
         <v>449</v>
       </c>
@@ -14236,7 +14239,7 @@
       </c>
     </row>
     <row r="173" spans="1:21" ht="13.8" hidden="1">
-      <c r="A173" s="109"/>
+      <c r="A173" s="101"/>
       <c r="B173" s="71" t="s">
         <v>456</v>
       </c>
@@ -14292,7 +14295,7 @@
       </c>
     </row>
     <row r="174" spans="1:21" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A174" s="95">
+      <c r="A174" s="92">
         <v>45</v>
       </c>
       <c r="B174" s="71" t="s">
@@ -14349,7 +14352,7 @@
       </c>
     </row>
     <row r="175" spans="1:21" ht="13.8" hidden="1">
-      <c r="A175" s="95"/>
+      <c r="A175" s="92"/>
       <c r="B175" s="71" t="s">
         <v>458</v>
       </c>
@@ -14405,7 +14408,7 @@
       </c>
     </row>
     <row r="176" spans="1:21" ht="13.8" hidden="1">
-      <c r="A176" s="95"/>
+      <c r="A176" s="92"/>
       <c r="B176" s="71" t="s">
         <v>458</v>
       </c>
@@ -14459,7 +14462,7 @@
       <c r="U176" s="71"/>
     </row>
     <row r="177" spans="1:21" ht="13.8" hidden="1">
-      <c r="A177" s="95"/>
+      <c r="A177" s="92"/>
       <c r="B177" s="71" t="s">
         <v>458</v>
       </c>
@@ -14515,7 +14518,7 @@
       </c>
     </row>
     <row r="178" spans="1:21" ht="27.6" hidden="1">
-      <c r="A178" s="95"/>
+      <c r="A178" s="92"/>
       <c r="B178" s="71" t="s">
         <v>458</v>
       </c>
@@ -14569,7 +14572,7 @@
       <c r="U178" s="71"/>
     </row>
     <row r="179" spans="1:21" ht="13.8" hidden="1">
-      <c r="A179" s="95"/>
+      <c r="A179" s="92"/>
       <c r="B179" s="71" t="s">
         <v>466</v>
       </c>
@@ -14625,7 +14628,7 @@
       </c>
     </row>
     <row r="180" spans="1:21" ht="13.8" hidden="1">
-      <c r="A180" s="95"/>
+      <c r="A180" s="92"/>
       <c r="B180" s="71" t="s">
         <v>468</v>
       </c>
@@ -14786,7 +14789,7 @@
       <c r="U182" s="66"/>
     </row>
     <row r="183" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A183" s="110">
+      <c r="A183" s="102">
         <v>46</v>
       </c>
       <c r="B183" s="71" t="s">
@@ -14840,7 +14843,7 @@
       </c>
     </row>
     <row r="184" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A184" s="110"/>
+      <c r="A184" s="102"/>
       <c r="B184" s="71" t="s">
         <v>471</v>
       </c>
@@ -14894,7 +14897,7 @@
       </c>
     </row>
     <row r="185" spans="1:21" ht="13.8" hidden="1">
-      <c r="A185" s="110"/>
+      <c r="A185" s="102"/>
       <c r="B185" s="71" t="s">
         <v>471</v>
       </c>
@@ -15008,7 +15011,7 @@
       </c>
     </row>
     <row r="187" spans="1:21" ht="13.8" hidden="1">
-      <c r="A187" s="108"/>
+      <c r="A187" s="100"/>
       <c r="B187" s="71" t="s">
         <v>483</v>
       </c>
@@ -15058,7 +15061,7 @@
       </c>
     </row>
     <row r="188" spans="1:21" ht="13.8" hidden="1">
-      <c r="A188" s="108"/>
+      <c r="A188" s="100"/>
       <c r="B188" s="71" t="s">
         <v>483</v>
       </c>
@@ -15110,7 +15113,7 @@
       <c r="U188" s="71"/>
     </row>
     <row r="189" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A189" s="109"/>
+      <c r="A189" s="101"/>
       <c r="B189" s="71" t="s">
         <v>483</v>
       </c>
@@ -15216,7 +15219,7 @@
       </c>
     </row>
     <row r="191" spans="1:21" ht="64.95" hidden="1" customHeight="1">
-      <c r="A191" s="95">
+      <c r="A191" s="92">
         <v>48</v>
       </c>
       <c r="B191" s="71" t="s">
@@ -15271,7 +15274,7 @@
       </c>
     </row>
     <row r="192" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A192" s="95"/>
+      <c r="A192" s="92"/>
       <c r="B192" s="71" t="s">
         <v>490</v>
       </c>
@@ -15324,7 +15327,7 @@
       </c>
     </row>
     <row r="193" spans="1:21" ht="13.8" hidden="1">
-      <c r="A193" s="95"/>
+      <c r="A193" s="92"/>
       <c r="B193" s="71" t="s">
         <v>490</v>
       </c>
@@ -15409,7 +15412,7 @@
       <c r="U194" s="66"/>
     </row>
     <row r="195" spans="1:21" ht="13.8" hidden="1">
-      <c r="A195" s="106"/>
+      <c r="A195" s="93"/>
       <c r="B195" s="71" t="s">
         <v>502</v>
       </c>
@@ -15463,7 +15466,7 @@
       </c>
     </row>
     <row r="196" spans="1:21" ht="24.6" hidden="1" customHeight="1">
-      <c r="A196" s="102"/>
+      <c r="A196" s="94"/>
       <c r="B196" s="71" t="s">
         <v>502</v>
       </c>
@@ -15517,7 +15520,7 @@
       </c>
     </row>
     <row r="197" spans="1:21" ht="13.8" hidden="1">
-      <c r="A197" s="95">
+      <c r="A197" s="92">
         <v>51</v>
       </c>
       <c r="B197" s="71" t="s">
@@ -15572,7 +15575,7 @@
       </c>
     </row>
     <row r="198" spans="1:21" ht="13.8" hidden="1">
-      <c r="A198" s="95"/>
+      <c r="A198" s="92"/>
       <c r="B198" s="71" t="s">
         <v>506</v>
       </c>
@@ -15628,7 +15631,7 @@
       </c>
     </row>
     <row r="199" spans="1:21" ht="13.8" hidden="1">
-      <c r="A199" s="95"/>
+      <c r="A199" s="92"/>
       <c r="B199" s="71" t="s">
         <v>506</v>
       </c>
@@ -15684,7 +15687,7 @@
       </c>
     </row>
     <row r="200" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A200" s="95"/>
+      <c r="A200" s="92"/>
       <c r="B200" s="71" t="s">
         <v>506</v>
       </c>
@@ -15899,7 +15902,7 @@
       </c>
     </row>
     <row r="204" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A204" s="95">
+      <c r="A204" s="92">
         <v>53</v>
       </c>
       <c r="B204" s="71" t="s">
@@ -15956,7 +15959,7 @@
       </c>
     </row>
     <row r="205" spans="1:21" ht="55.2" hidden="1">
-      <c r="A205" s="95"/>
+      <c r="A205" s="92"/>
       <c r="B205" s="71" t="s">
         <v>518</v>
       </c>
@@ -16012,7 +16015,7 @@
       </c>
     </row>
     <row r="206" spans="1:21" ht="13.8" hidden="1">
-      <c r="A206" s="95"/>
+      <c r="A206" s="92"/>
       <c r="B206" s="66" t="s">
         <v>522</v>
       </c>
@@ -16068,7 +16071,7 @@
       </c>
     </row>
     <row r="207" spans="1:21" ht="13.8" hidden="1">
-      <c r="A207" s="95">
+      <c r="A207" s="92">
         <v>54</v>
       </c>
       <c r="B207" s="71" t="s">
@@ -16124,7 +16127,7 @@
       </c>
     </row>
     <row r="208" spans="1:21" ht="13.8" hidden="1">
-      <c r="A208" s="95"/>
+      <c r="A208" s="92"/>
       <c r="B208" s="71" t="s">
         <v>525</v>
       </c>
@@ -16182,7 +16185,7 @@
       </c>
     </row>
     <row r="209" spans="1:21" ht="32.4" hidden="1" customHeight="1">
-      <c r="A209" s="95">
+      <c r="A209" s="92">
         <v>55</v>
       </c>
       <c r="B209" s="71" t="s">
@@ -16239,7 +16242,7 @@
       </c>
     </row>
     <row r="210" spans="1:21" ht="13.8" hidden="1">
-      <c r="A210" s="95"/>
+      <c r="A210" s="92"/>
       <c r="B210" s="71" t="s">
         <v>528</v>
       </c>
@@ -16293,7 +16296,7 @@
       <c r="U210" s="71"/>
     </row>
     <row r="211" spans="1:21" ht="16.2" hidden="1" customHeight="1">
-      <c r="A211" s="95"/>
+      <c r="A211" s="92"/>
       <c r="B211" s="71" t="s">
         <v>528</v>
       </c>
@@ -16347,7 +16350,7 @@
       <c r="U211" s="66"/>
     </row>
     <row r="212" spans="1:21" ht="80.400000000000006" hidden="1" customHeight="1">
-      <c r="A212" s="95">
+      <c r="A212" s="92">
         <v>56</v>
       </c>
       <c r="B212" s="71" t="s">
@@ -16402,7 +16405,7 @@
       </c>
     </row>
     <row r="213" spans="1:21" ht="13.8" hidden="1">
-      <c r="A213" s="95"/>
+      <c r="A213" s="92"/>
       <c r="B213" s="71" t="s">
         <v>537</v>
       </c>
@@ -16460,7 +16463,7 @@
       </c>
     </row>
     <row r="214" spans="1:21" ht="27.6" hidden="1">
-      <c r="A214" s="107">
+      <c r="A214" s="99">
         <v>57</v>
       </c>
       <c r="B214" s="71" t="s">
@@ -16515,7 +16518,7 @@
       </c>
     </row>
     <row r="215" spans="1:21" ht="13.8" hidden="1">
-      <c r="A215" s="108"/>
+      <c r="A215" s="100"/>
       <c r="B215" s="71" t="s">
         <v>539</v>
       </c>
@@ -16571,7 +16574,7 @@
       </c>
     </row>
     <row r="216" spans="1:21" ht="13.8" hidden="1">
-      <c r="A216" s="108"/>
+      <c r="A216" s="100"/>
       <c r="B216" s="71" t="s">
         <v>539</v>
       </c>
@@ -16627,7 +16630,7 @@
       </c>
     </row>
     <row r="217" spans="1:21" ht="41.4" hidden="1">
-      <c r="A217" s="106"/>
+      <c r="A217" s="93"/>
       <c r="B217" s="71" t="s">
         <v>539</v>
       </c>
@@ -16683,7 +16686,7 @@
       </c>
     </row>
     <row r="218" spans="1:21" ht="13.8" hidden="1">
-      <c r="A218" s="109"/>
+      <c r="A218" s="101"/>
       <c r="B218" s="71" t="s">
         <v>539</v>
       </c>
@@ -16962,7 +16965,7 @@
       </c>
     </row>
     <row r="223" spans="1:21" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A223" s="95">
+      <c r="A223" s="92">
         <v>59</v>
       </c>
       <c r="B223" s="71" t="s">
@@ -17017,7 +17020,7 @@
       </c>
     </row>
     <row r="224" spans="1:21" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A224" s="95"/>
+      <c r="A224" s="92"/>
       <c r="B224" s="71" t="s">
         <v>560</v>
       </c>
@@ -17073,7 +17076,7 @@
       </c>
     </row>
     <row r="225" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A225" s="95"/>
+      <c r="A225" s="92"/>
       <c r="B225" s="71" t="s">
         <v>560</v>
       </c>
@@ -17124,7 +17127,7 @@
       <c r="U225" s="71"/>
     </row>
     <row r="226" spans="1:21" ht="13.8" hidden="1">
-      <c r="A226" s="95"/>
+      <c r="A226" s="92"/>
       <c r="B226" s="71" t="s">
         <v>560</v>
       </c>
@@ -17180,7 +17183,7 @@
       </c>
     </row>
     <row r="227" spans="1:21" ht="27.6" hidden="1">
-      <c r="A227" s="95"/>
+      <c r="A227" s="92"/>
       <c r="B227" s="71" t="s">
         <v>560</v>
       </c>
@@ -17232,7 +17235,7 @@
       <c r="U227" s="66"/>
     </row>
     <row r="228" spans="1:21" ht="13.8" hidden="1">
-      <c r="A228" s="95"/>
+      <c r="A228" s="92"/>
       <c r="B228" s="71" t="s">
         <v>560</v>
       </c>
@@ -17590,7 +17593,7 @@
       </c>
     </row>
     <row r="235" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A235" s="101">
+      <c r="A235" s="98">
         <v>63</v>
       </c>
       <c r="B235" s="71" t="s">
@@ -17644,7 +17647,7 @@
       </c>
     </row>
     <row r="236" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A236" s="106"/>
+      <c r="A236" s="93"/>
       <c r="B236" s="71" t="s">
         <v>581</v>
       </c>
@@ -17698,7 +17701,7 @@
       </c>
     </row>
     <row r="237" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A237" s="106"/>
+      <c r="A237" s="93"/>
       <c r="B237" s="71" t="s">
         <v>581</v>
       </c>
@@ -17752,7 +17755,7 @@
       </c>
     </row>
     <row r="238" spans="1:21" ht="39.6" hidden="1" customHeight="1">
-      <c r="A238" s="106"/>
+      <c r="A238" s="93"/>
       <c r="B238" s="71" t="s">
         <v>581</v>
       </c>
@@ -17807,7 +17810,7 @@
       </c>
     </row>
     <row r="239" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A239" s="106"/>
+      <c r="A239" s="93"/>
       <c r="B239" s="71" t="s">
         <v>581</v>
       </c>
@@ -17862,7 +17865,7 @@
       </c>
     </row>
     <row r="240" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A240" s="102"/>
+      <c r="A240" s="94"/>
       <c r="B240" s="71" t="s">
         <v>595</v>
       </c>
@@ -17914,7 +17917,7 @@
       </c>
     </row>
     <row r="241" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A241" s="95">
+      <c r="A241" s="92">
         <v>64</v>
       </c>
       <c r="B241" s="71" t="s">
@@ -17969,7 +17972,7 @@
       <c r="U241" s="71"/>
     </row>
     <row r="242" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A242" s="95"/>
+      <c r="A242" s="92"/>
       <c r="B242" s="71" t="s">
         <v>598</v>
       </c>
@@ -18023,7 +18026,7 @@
       </c>
     </row>
     <row r="243" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A243" s="95"/>
+      <c r="A243" s="92"/>
       <c r="B243" s="71" t="s">
         <v>598</v>
       </c>
@@ -18083,7 +18086,7 @@
       </c>
     </row>
     <row r="244" spans="1:21" ht="41.4" hidden="1">
-      <c r="A244" s="95"/>
+      <c r="A244" s="92"/>
       <c r="B244" s="71" t="s">
         <v>598</v>
       </c>
@@ -18135,7 +18138,7 @@
       </c>
     </row>
     <row r="245" spans="1:21" ht="13.8" hidden="1">
-      <c r="A245" s="95"/>
+      <c r="A245" s="92"/>
       <c r="B245" s="71" t="s">
         <v>598</v>
       </c>
@@ -18170,7 +18173,7 @@
       <c r="U245" s="71"/>
     </row>
     <row r="246" spans="1:21" ht="13.8" hidden="1">
-      <c r="A246" s="95"/>
+      <c r="A246" s="92"/>
       <c r="B246" s="71" t="s">
         <v>598</v>
       </c>
@@ -18222,7 +18225,7 @@
       </c>
     </row>
     <row r="247" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A247" s="95"/>
+      <c r="A247" s="92"/>
       <c r="B247" s="71" t="s">
         <v>598</v>
       </c>
@@ -18331,7 +18334,7 @@
       <c r="U248" s="71"/>
     </row>
     <row r="249" spans="1:21" ht="81.599999999999994" customHeight="1">
-      <c r="A249" s="95">
+      <c r="A249" s="92">
         <v>65</v>
       </c>
       <c r="B249" s="71" t="s">
@@ -18343,7 +18346,9 @@
       <c r="D249" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="E249" s="81"/>
+      <c r="E249" s="81" t="s">
+        <v>1072</v>
+      </c>
       <c r="F249" s="71" t="s">
         <v>611</v>
       </c>
@@ -18376,7 +18381,7 @@
         <v>2025</v>
       </c>
       <c r="Q249" s="66" t="s">
-        <v>74</v>
+        <v>385</v>
       </c>
       <c r="R249" s="66"/>
       <c r="S249" s="66"/>
@@ -18386,7 +18391,7 @@
       </c>
     </row>
     <row r="250" spans="1:21" ht="81.599999999999994" customHeight="1">
-      <c r="A250" s="95"/>
+      <c r="A250" s="92"/>
       <c r="B250" s="71" t="s">
         <v>606</v>
       </c>
@@ -18442,7 +18447,7 @@
       </c>
     </row>
     <row r="251" spans="1:21" ht="40.950000000000003" customHeight="1">
-      <c r="A251" s="95"/>
+      <c r="A251" s="92"/>
       <c r="B251" s="71" t="s">
         <v>606</v>
       </c>
@@ -18632,7 +18637,7 @@
       <c r="U254" s="66"/>
     </row>
     <row r="255" spans="1:21" ht="27.6" hidden="1">
-      <c r="A255" s="101">
+      <c r="A255" s="98">
         <v>68</v>
       </c>
       <c r="B255" s="71" t="s">
@@ -18686,7 +18691,7 @@
       </c>
     </row>
     <row r="256" spans="1:21" ht="27.6" hidden="1">
-      <c r="A256" s="106"/>
+      <c r="A256" s="93"/>
       <c r="B256" s="71" t="s">
         <v>619</v>
       </c>
@@ -18741,7 +18746,7 @@
       </c>
     </row>
     <row r="257" spans="1:21" ht="13.8" hidden="1">
-      <c r="A257" s="106"/>
+      <c r="A257" s="93"/>
       <c r="B257" s="71" t="s">
         <v>619</v>
       </c>
@@ -18797,7 +18802,7 @@
       </c>
     </row>
     <row r="258" spans="1:21" ht="13.8" hidden="1">
-      <c r="A258" s="106"/>
+      <c r="A258" s="93"/>
       <c r="B258" s="71" t="s">
         <v>619</v>
       </c>
@@ -18853,7 +18858,7 @@
       </c>
     </row>
     <row r="259" spans="1:21" ht="13.8" hidden="1">
-      <c r="A259" s="106"/>
+      <c r="A259" s="93"/>
       <c r="B259" s="71" t="s">
         <v>619</v>
       </c>
@@ -18907,7 +18912,7 @@
       </c>
     </row>
     <row r="260" spans="1:21" ht="34.200000000000003" hidden="1" customHeight="1">
-      <c r="A260" s="102"/>
+      <c r="A260" s="94"/>
       <c r="B260" s="71" t="s">
         <v>619</v>
       </c>
@@ -18963,7 +18968,7 @@
       </c>
     </row>
     <row r="261" spans="1:21" ht="55.2" hidden="1">
-      <c r="A261" s="101">
+      <c r="A261" s="98">
         <v>69</v>
       </c>
       <c r="B261" s="71" t="s">
@@ -19018,7 +19023,7 @@
       </c>
     </row>
     <row r="262" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A262" s="106"/>
+      <c r="A262" s="93"/>
       <c r="B262" s="71" t="s">
         <v>629</v>
       </c>
@@ -19070,7 +19075,7 @@
       </c>
     </row>
     <row r="263" spans="1:21" ht="102" hidden="1" customHeight="1">
-      <c r="A263" s="106"/>
+      <c r="A263" s="93"/>
       <c r="B263" s="71" t="s">
         <v>637</v>
       </c>
@@ -19118,7 +19123,7 @@
       </c>
     </row>
     <row r="264" spans="1:21" ht="55.2" hidden="1">
-      <c r="A264" s="106"/>
+      <c r="A264" s="93"/>
       <c r="B264" s="71" t="s">
         <v>637</v>
       </c>
@@ -19168,7 +19173,7 @@
       </c>
     </row>
     <row r="265" spans="1:21" ht="46.2" hidden="1" customHeight="1">
-      <c r="A265" s="106"/>
+      <c r="A265" s="93"/>
       <c r="B265" s="71" t="s">
         <v>629</v>
       </c>
@@ -19279,7 +19284,7 @@
       <c r="U266" s="71"/>
     </row>
     <row r="267" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A267" s="95">
+      <c r="A267" s="92">
         <v>70</v>
       </c>
       <c r="B267" s="71" t="s">
@@ -19337,7 +19342,7 @@
       <c r="U267" s="71"/>
     </row>
     <row r="268" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A268" s="95"/>
+      <c r="A268" s="92"/>
       <c r="B268" s="71" t="s">
         <v>643</v>
       </c>
@@ -19393,7 +19398,7 @@
       <c r="U268" s="71"/>
     </row>
     <row r="269" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A269" s="95"/>
+      <c r="A269" s="92"/>
       <c r="B269" s="71" t="s">
         <v>643</v>
       </c>
@@ -19449,7 +19454,7 @@
       <c r="U269" s="71"/>
     </row>
     <row r="270" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A270" s="95"/>
+      <c r="A270" s="92"/>
       <c r="B270" s="71" t="s">
         <v>643</v>
       </c>
@@ -19561,7 +19566,7 @@
       </c>
     </row>
     <row r="272" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A272" s="95">
+      <c r="A272" s="92">
         <v>71</v>
       </c>
       <c r="B272" s="71" t="s">
@@ -19617,7 +19622,7 @@
       <c r="U272" s="71"/>
     </row>
     <row r="273" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A273" s="95"/>
+      <c r="A273" s="92"/>
       <c r="B273" s="71" t="s">
         <v>653</v>
       </c>
@@ -19673,7 +19678,7 @@
       </c>
     </row>
     <row r="274" spans="1:21" ht="13.8" hidden="1">
-      <c r="A274" s="95"/>
+      <c r="A274" s="92"/>
       <c r="B274" s="71" t="s">
         <v>653</v>
       </c>
@@ -19729,7 +19734,7 @@
       </c>
     </row>
     <row r="275" spans="1:21" ht="13.8" hidden="1">
-      <c r="A275" s="95"/>
+      <c r="A275" s="92"/>
       <c r="B275" s="71" t="s">
         <v>653</v>
       </c>
@@ -19785,7 +19790,7 @@
       </c>
     </row>
     <row r="276" spans="1:21" ht="13.8" hidden="1">
-      <c r="A276" s="95"/>
+      <c r="A276" s="92"/>
       <c r="B276" s="66" t="s">
         <v>660</v>
       </c>
@@ -20061,7 +20066,7 @@
       <c r="U280" s="66"/>
     </row>
     <row r="281" spans="1:21" ht="27.6" hidden="1">
-      <c r="A281" s="95">
+      <c r="A281" s="92">
         <v>74</v>
       </c>
       <c r="B281" s="71" t="s">
@@ -20115,7 +20120,7 @@
       </c>
     </row>
     <row r="282" spans="1:21" ht="13.8" hidden="1">
-      <c r="A282" s="95"/>
+      <c r="A282" s="92"/>
       <c r="B282" s="71" t="s">
         <v>669</v>
       </c>
@@ -20164,7 +20169,7 @@
       <c r="U282" s="66"/>
     </row>
     <row r="283" spans="1:21" ht="37.200000000000003" hidden="1" customHeight="1">
-      <c r="A283" s="95">
+      <c r="A283" s="92">
         <v>75</v>
       </c>
       <c r="B283" s="71" t="s">
@@ -20219,7 +20224,7 @@
       </c>
     </row>
     <row r="284" spans="1:21" ht="13.8" hidden="1">
-      <c r="A284" s="95"/>
+      <c r="A284" s="92"/>
       <c r="B284" s="71" t="s">
         <v>672</v>
       </c>
@@ -20273,7 +20278,7 @@
       <c r="U284" s="71"/>
     </row>
     <row r="285" spans="1:21" ht="13.8" hidden="1">
-      <c r="A285" s="102">
+      <c r="A285" s="94">
         <v>76</v>
       </c>
       <c r="B285" s="71" t="s">
@@ -20331,7 +20336,7 @@
       </c>
     </row>
     <row r="286" spans="1:21" ht="13.8" hidden="1">
-      <c r="A286" s="102"/>
+      <c r="A286" s="94"/>
       <c r="B286" s="71" t="s">
         <v>676</v>
       </c>
@@ -20387,7 +20392,7 @@
       </c>
     </row>
     <row r="287" spans="1:21" ht="13.8" hidden="1">
-      <c r="A287" s="102"/>
+      <c r="A287" s="94"/>
       <c r="B287" s="71" t="s">
         <v>676</v>
       </c>
@@ -20443,7 +20448,7 @@
       </c>
     </row>
     <row r="288" spans="1:21" ht="13.8" hidden="1">
-      <c r="A288" s="102"/>
+      <c r="A288" s="94"/>
       <c r="B288" s="71" t="s">
         <v>676</v>
       </c>
@@ -20499,7 +20504,7 @@
       </c>
     </row>
     <row r="289" spans="1:21" ht="13.8" hidden="1">
-      <c r="A289" s="95"/>
+      <c r="A289" s="92"/>
       <c r="B289" s="71" t="s">
         <v>676</v>
       </c>
@@ -20552,7 +20557,7 @@
       </c>
     </row>
     <row r="290" spans="1:21" ht="27.6" hidden="1">
-      <c r="A290" s="95"/>
+      <c r="A290" s="92"/>
       <c r="B290" s="71" t="s">
         <v>676</v>
       </c>
@@ -20606,7 +20611,7 @@
       </c>
     </row>
     <row r="291" spans="1:21" ht="13.8" hidden="1">
-      <c r="A291" s="95"/>
+      <c r="A291" s="92"/>
       <c r="B291" s="71" t="s">
         <v>676</v>
       </c>
@@ -20662,7 +20667,7 @@
       </c>
     </row>
     <row r="292" spans="1:21" ht="13.8" hidden="1">
-      <c r="A292" s="95"/>
+      <c r="A292" s="92"/>
       <c r="B292" s="71" t="s">
         <v>676</v>
       </c>
@@ -20714,7 +20719,7 @@
       <c r="U292" s="71"/>
     </row>
     <row r="293" spans="1:21" ht="13.8" hidden="1">
-      <c r="A293" s="95"/>
+      <c r="A293" s="92"/>
       <c r="B293" s="71" t="s">
         <v>676</v>
       </c>
@@ -20828,7 +20833,7 @@
       </c>
     </row>
     <row r="295" spans="1:21" ht="96.6" hidden="1">
-      <c r="A295" s="95">
+      <c r="A295" s="92">
         <v>77</v>
       </c>
       <c r="B295" s="71" t="s">
@@ -20890,7 +20895,7 @@
       </c>
     </row>
     <row r="296" spans="1:21" ht="27.6" hidden="1">
-      <c r="A296" s="95"/>
+      <c r="A296" s="92"/>
       <c r="B296" s="71" t="s">
         <v>691</v>
       </c>
@@ -20950,7 +20955,7 @@
       </c>
     </row>
     <row r="297" spans="1:21" ht="13.8" hidden="1">
-      <c r="A297" s="95"/>
+      <c r="A297" s="92"/>
       <c r="B297" s="71" t="s">
         <v>691</v>
       </c>
@@ -21010,7 +21015,7 @@
       </c>
     </row>
     <row r="298" spans="1:21" ht="27.6" hidden="1">
-      <c r="A298" s="95">
+      <c r="A298" s="92">
         <v>78</v>
       </c>
       <c r="B298" s="71" t="s">
@@ -21065,7 +21070,7 @@
       </c>
     </row>
     <row r="299" spans="1:21" ht="13.8" hidden="1">
-      <c r="A299" s="95"/>
+      <c r="A299" s="92"/>
       <c r="B299" s="71" t="s">
         <v>702</v>
       </c>
@@ -21119,7 +21124,7 @@
       <c r="U299" s="71"/>
     </row>
     <row r="300" spans="1:21" ht="13.8" hidden="1">
-      <c r="A300" s="95"/>
+      <c r="A300" s="92"/>
       <c r="B300" s="71" t="s">
         <v>702</v>
       </c>
@@ -21175,7 +21180,7 @@
       </c>
     </row>
     <row r="301" spans="1:21" ht="13.8" hidden="1">
-      <c r="A301" s="106"/>
+      <c r="A301" s="93"/>
       <c r="B301" s="71" t="s">
         <v>637</v>
       </c>
@@ -21229,7 +21234,7 @@
       <c r="U301" s="71"/>
     </row>
     <row r="302" spans="1:21" ht="13.8" hidden="1">
-      <c r="A302" s="102"/>
+      <c r="A302" s="94"/>
       <c r="B302" s="71" t="s">
         <v>637</v>
       </c>
@@ -21285,7 +21290,7 @@
       </c>
     </row>
     <row r="303" spans="1:21" ht="27.6" hidden="1">
-      <c r="A303" s="101">
+      <c r="A303" s="98">
         <v>80</v>
       </c>
       <c r="B303" s="71" t="s">
@@ -21340,7 +21345,7 @@
       </c>
     </row>
     <row r="304" spans="1:21" ht="13.8" hidden="1">
-      <c r="A304" s="106"/>
+      <c r="A304" s="93"/>
       <c r="B304" s="71" t="s">
         <v>716</v>
       </c>
@@ -21394,7 +21399,7 @@
       <c r="U304" s="71"/>
     </row>
     <row r="305" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A305" s="101">
+      <c r="A305" s="98">
         <v>81</v>
       </c>
       <c r="B305" s="71" t="s">
@@ -21448,7 +21453,7 @@
       </c>
     </row>
     <row r="306" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A306" s="106"/>
+      <c r="A306" s="93"/>
       <c r="B306" s="71" t="s">
         <v>718</v>
       </c>
@@ -21502,7 +21507,7 @@
       </c>
     </row>
     <row r="307" spans="1:21" ht="81.599999999999994" hidden="1" customHeight="1">
-      <c r="A307" s="106"/>
+      <c r="A307" s="93"/>
       <c r="B307" s="71" t="s">
         <v>718</v>
       </c>
@@ -21555,7 +21560,7 @@
       </c>
     </row>
     <row r="308" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A308" s="102"/>
+      <c r="A308" s="94"/>
       <c r="B308" s="71" t="s">
         <v>718</v>
       </c>
@@ -21681,56 +21686,56 @@
       <c r="D310" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="E310" s="103">
+      <c r="E310" s="104">
         <v>4600018191</v>
       </c>
-      <c r="F310" s="112" t="s">
+      <c r="F310" s="103" t="s">
         <v>729</v>
       </c>
-      <c r="G310" s="95" t="s">
+      <c r="G310" s="92" t="s">
         <v>730</v>
       </c>
-      <c r="H310" s="95">
+      <c r="H310" s="92">
         <v>13.3</v>
       </c>
-      <c r="I310" s="101" t="s">
+      <c r="I310" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="J310" s="101" t="s">
+      <c r="J310" s="98" t="s">
         <v>540</v>
       </c>
-      <c r="K310" s="99">
+      <c r="K310" s="95">
         <f>806037831+182039258</f>
         <v>988077089</v>
       </c>
-      <c r="L310" s="99">
+      <c r="L310" s="95">
         <v>0</v>
       </c>
-      <c r="M310" s="99">
+      <c r="M310" s="95">
         <f>+K310</f>
         <v>988077089</v>
       </c>
-      <c r="N310" s="96" t="s">
+      <c r="N310" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="O310" s="96" t="s">
+      <c r="O310" s="97" t="s">
         <v>731</v>
       </c>
-      <c r="P310" s="95">
+      <c r="P310" s="92">
         <v>2025</v>
       </c>
-      <c r="Q310" s="96" t="s">
+      <c r="Q310" s="97" t="s">
         <v>37</v>
       </c>
       <c r="R310" s="71"/>
       <c r="S310" s="71"/>
-      <c r="T310" s="95"/>
-      <c r="U310" s="95" t="s">
+      <c r="T310" s="92"/>
+      <c r="U310" s="92" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="311" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A311" s="95">
+      <c r="A311" s="92">
         <v>84</v>
       </c>
       <c r="B311" s="71" t="s">
@@ -21742,26 +21747,26 @@
       <c r="D311" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="E311" s="104"/>
-      <c r="F311" s="96"/>
-      <c r="G311" s="95"/>
-      <c r="H311" s="95"/>
-      <c r="I311" s="102"/>
-      <c r="J311" s="102"/>
-      <c r="K311" s="99"/>
-      <c r="L311" s="99"/>
-      <c r="M311" s="99"/>
-      <c r="N311" s="96"/>
-      <c r="O311" s="96"/>
-      <c r="P311" s="95"/>
-      <c r="Q311" s="96"/>
+      <c r="E311" s="105"/>
+      <c r="F311" s="97"/>
+      <c r="G311" s="92"/>
+      <c r="H311" s="92"/>
+      <c r="I311" s="94"/>
+      <c r="J311" s="94"/>
+      <c r="K311" s="95"/>
+      <c r="L311" s="95"/>
+      <c r="M311" s="95"/>
+      <c r="N311" s="97"/>
+      <c r="O311" s="97"/>
+      <c r="P311" s="92"/>
+      <c r="Q311" s="97"/>
       <c r="R311" s="71"/>
       <c r="S311" s="71"/>
-      <c r="T311" s="95"/>
-      <c r="U311" s="95"/>
+      <c r="T311" s="92"/>
+      <c r="U311" s="92"/>
     </row>
     <row r="312" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A312" s="95"/>
+      <c r="A312" s="92"/>
       <c r="B312" s="71" t="s">
         <v>728</v>
       </c>
@@ -21771,57 +21776,57 @@
       <c r="D312" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="E312" s="103">
+      <c r="E312" s="104">
         <v>4600009793</v>
       </c>
-      <c r="F312" s="96" t="s">
+      <c r="F312" s="97" t="s">
         <v>733</v>
       </c>
-      <c r="G312" s="95" t="s">
+      <c r="G312" s="92" t="s">
         <v>734</v>
       </c>
-      <c r="H312" s="95">
+      <c r="H312" s="92">
         <v>31.12</v>
       </c>
-      <c r="I312" s="101" t="s">
+      <c r="I312" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="J312" s="101" t="s">
+      <c r="J312" s="98" t="s">
         <v>54</v>
       </c>
-      <c r="K312" s="99">
+      <c r="K312" s="95">
         <f>+M312</f>
         <v>73907566008</v>
       </c>
-      <c r="L312" s="99">
+      <c r="L312" s="95">
         <v>0</v>
       </c>
-      <c r="M312" s="99">
+      <c r="M312" s="95">
         <v>73907566008</v>
       </c>
-      <c r="N312" s="96" t="s">
+      <c r="N312" s="97" t="s">
         <v>735</v>
       </c>
-      <c r="O312" s="96" t="s">
+      <c r="O312" s="97" t="s">
         <v>97</v>
       </c>
-      <c r="P312" s="95">
+      <c r="P312" s="92">
         <v>2019</v>
       </c>
-      <c r="Q312" s="96" t="s">
+      <c r="Q312" s="97" t="s">
         <v>51</v>
       </c>
       <c r="R312" s="71"/>
       <c r="S312" s="71"/>
-      <c r="T312" s="113">
+      <c r="T312" s="96">
         <v>1</v>
       </c>
-      <c r="U312" s="95" t="s">
+      <c r="U312" s="92" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="313" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A313" s="95"/>
+      <c r="A313" s="92"/>
       <c r="B313" s="71" t="s">
         <v>732</v>
       </c>
@@ -21831,26 +21836,26 @@
       <c r="D313" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="E313" s="104"/>
-      <c r="F313" s="96"/>
-      <c r="G313" s="95"/>
-      <c r="H313" s="95"/>
-      <c r="I313" s="102"/>
-      <c r="J313" s="102"/>
-      <c r="K313" s="99"/>
-      <c r="L313" s="99"/>
-      <c r="M313" s="99"/>
-      <c r="N313" s="96"/>
-      <c r="O313" s="96"/>
-      <c r="P313" s="95"/>
-      <c r="Q313" s="96"/>
+      <c r="E313" s="105"/>
+      <c r="F313" s="97"/>
+      <c r="G313" s="92"/>
+      <c r="H313" s="92"/>
+      <c r="I313" s="94"/>
+      <c r="J313" s="94"/>
+      <c r="K313" s="95"/>
+      <c r="L313" s="95"/>
+      <c r="M313" s="95"/>
+      <c r="N313" s="97"/>
+      <c r="O313" s="97"/>
+      <c r="P313" s="92"/>
+      <c r="Q313" s="97"/>
       <c r="R313" s="71"/>
       <c r="S313" s="71"/>
-      <c r="T313" s="113"/>
-      <c r="U313" s="95"/>
+      <c r="T313" s="96"/>
+      <c r="U313" s="92"/>
     </row>
     <row r="314" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A314" s="95"/>
+      <c r="A314" s="92"/>
       <c r="B314" s="71" t="s">
         <v>732</v>
       </c>
@@ -21908,7 +21913,7 @@
       </c>
     </row>
     <row r="315" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A315" s="95"/>
+      <c r="A315" s="92"/>
       <c r="B315" s="71" t="s">
         <v>732</v>
       </c>
@@ -21964,7 +21969,7 @@
       <c r="U315" s="71"/>
     </row>
     <row r="316" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A316" s="95"/>
+      <c r="A316" s="92"/>
       <c r="B316" s="71" t="s">
         <v>732</v>
       </c>
@@ -22118,7 +22123,7 @@
       </c>
     </row>
     <row r="319" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A319" s="101">
+      <c r="A319" s="98">
         <v>85</v>
       </c>
       <c r="B319" s="71" t="s">
@@ -22167,7 +22172,7 @@
       <c r="U319" s="71"/>
     </row>
     <row r="320" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A320" s="102"/>
+      <c r="A320" s="94"/>
       <c r="B320" s="71" t="s">
         <v>738</v>
       </c>
@@ -22220,7 +22225,7 @@
       </c>
     </row>
     <row r="321" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A321" s="107">
+      <c r="A321" s="99">
         <v>86</v>
       </c>
       <c r="B321" s="71" t="s">
@@ -22274,7 +22279,7 @@
       </c>
     </row>
     <row r="322" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A322" s="108"/>
+      <c r="A322" s="100"/>
       <c r="B322" s="66" t="s">
         <v>744</v>
       </c>
@@ -22324,7 +22329,7 @@
       </c>
     </row>
     <row r="323" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A323" s="108"/>
+      <c r="A323" s="100"/>
       <c r="B323" s="66" t="s">
         <v>744</v>
       </c>
@@ -22378,7 +22383,7 @@
       </c>
     </row>
     <row r="324" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A324" s="108"/>
+      <c r="A324" s="100"/>
       <c r="B324" s="66" t="s">
         <v>744</v>
       </c>
@@ -22432,7 +22437,7 @@
       </c>
     </row>
     <row r="325" spans="1:21" ht="93" hidden="1" customHeight="1">
-      <c r="A325" s="106"/>
+      <c r="A325" s="93"/>
       <c r="B325" s="66" t="s">
         <v>744</v>
       </c>
@@ -22484,7 +22489,7 @@
       </c>
     </row>
     <row r="326" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A326" s="106"/>
+      <c r="A326" s="93"/>
       <c r="B326" s="66" t="s">
         <v>744</v>
       </c>
@@ -22536,7 +22541,7 @@
       </c>
     </row>
     <row r="327" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A327" s="108"/>
+      <c r="A327" s="100"/>
       <c r="B327" s="66" t="s">
         <v>744</v>
       </c>
@@ -22592,7 +22597,7 @@
       </c>
     </row>
     <row r="328" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A328" s="108"/>
+      <c r="A328" s="100"/>
       <c r="B328" s="71" t="s">
         <v>744</v>
       </c>
@@ -22644,7 +22649,7 @@
       </c>
     </row>
     <row r="329" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A329" s="108"/>
+      <c r="A329" s="100"/>
       <c r="B329" s="71" t="s">
         <v>744</v>
       </c>
@@ -22698,7 +22703,7 @@
       <c r="U329" s="71"/>
     </row>
     <row r="330" spans="1:21" ht="13.8" hidden="1">
-      <c r="A330" s="109"/>
+      <c r="A330" s="101"/>
       <c r="B330" s="71" t="s">
         <v>744</v>
       </c>
@@ -22930,7 +22935,7 @@
       </c>
     </row>
     <row r="335" spans="1:21" ht="41.4" hidden="1">
-      <c r="A335" s="101">
+      <c r="A335" s="98">
         <v>89</v>
       </c>
       <c r="B335" s="71" t="s">
@@ -22992,7 +22997,7 @@
       </c>
     </row>
     <row r="336" spans="1:21" ht="44.4" hidden="1" customHeight="1">
-      <c r="A336" s="106"/>
+      <c r="A336" s="93"/>
       <c r="B336" s="71" t="s">
         <v>765</v>
       </c>
@@ -23045,7 +23050,7 @@
       </c>
     </row>
     <row r="337" spans="1:22" ht="155.4" hidden="1" customHeight="1">
-      <c r="A337" s="106"/>
+      <c r="A337" s="93"/>
       <c r="B337" s="71" t="s">
         <v>765</v>
       </c>
@@ -23098,7 +23103,7 @@
       </c>
     </row>
     <row r="338" spans="1:22" ht="13.8" hidden="1">
-      <c r="A338" s="102"/>
+      <c r="A338" s="94"/>
       <c r="B338" s="71" t="s">
         <v>765</v>
       </c>
@@ -23200,7 +23205,7 @@
       </c>
     </row>
     <row r="340" spans="1:22" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A340" s="95">
+      <c r="A340" s="92">
         <v>90</v>
       </c>
       <c r="B340" s="71" t="s">
@@ -23258,7 +23263,7 @@
       <c r="V340" s="33"/>
     </row>
     <row r="341" spans="1:22" ht="20.399999999999999" hidden="1" customHeight="1">
-      <c r="A341" s="95"/>
+      <c r="A341" s="92"/>
       <c r="B341" s="71" t="s">
         <v>773</v>
       </c>
@@ -23313,7 +23318,7 @@
       <c r="V341" s="33"/>
     </row>
     <row r="342" spans="1:22" ht="13.8" hidden="1">
-      <c r="A342" s="95">
+      <c r="A342" s="92">
         <v>91</v>
       </c>
       <c r="B342" s="71" t="s">
@@ -23371,7 +23376,7 @@
       </c>
     </row>
     <row r="343" spans="1:22" ht="13.8" hidden="1">
-      <c r="A343" s="95"/>
+      <c r="A343" s="92"/>
       <c r="B343" s="71" t="s">
         <v>776</v>
       </c>
@@ -23427,7 +23432,7 @@
       </c>
     </row>
     <row r="344" spans="1:22" ht="27.6" hidden="1">
-      <c r="A344" s="95"/>
+      <c r="A344" s="92"/>
       <c r="B344" s="71" t="s">
         <v>776</v>
       </c>
@@ -23479,7 +23484,7 @@
       </c>
     </row>
     <row r="345" spans="1:22" ht="13.8" hidden="1">
-      <c r="A345" s="95"/>
+      <c r="A345" s="92"/>
       <c r="B345" s="71" t="s">
         <v>776</v>
       </c>
@@ -23535,7 +23540,7 @@
       </c>
     </row>
     <row r="346" spans="1:22" ht="27.6" hidden="1">
-      <c r="A346" s="95"/>
+      <c r="A346" s="92"/>
       <c r="B346" s="71" t="s">
         <v>776</v>
       </c>
@@ -23588,7 +23593,7 @@
       </c>
     </row>
     <row r="347" spans="1:22" ht="27.6" hidden="1">
-      <c r="A347" s="95"/>
+      <c r="A347" s="92"/>
       <c r="B347" s="71" t="s">
         <v>776</v>
       </c>
@@ -23634,7 +23639,7 @@
       </c>
     </row>
     <row r="348" spans="1:22" ht="13.8" hidden="1">
-      <c r="A348" s="95"/>
+      <c r="A348" s="92"/>
       <c r="B348" s="71" t="s">
         <v>776</v>
       </c>
@@ -23690,7 +23695,7 @@
       </c>
     </row>
     <row r="349" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A349" s="95">
+      <c r="A349" s="92">
         <v>92</v>
       </c>
       <c r="B349" s="71" t="s">
@@ -23747,7 +23752,7 @@
       <c r="U349" s="71"/>
     </row>
     <row r="350" spans="1:22" ht="61.2" hidden="1" customHeight="1">
-      <c r="A350" s="95"/>
+      <c r="A350" s="92"/>
       <c r="B350" s="71" t="s">
         <v>788</v>
       </c>
@@ -23801,7 +23806,7 @@
       </c>
     </row>
     <row r="351" spans="1:22" ht="13.8" hidden="1">
-      <c r="A351" s="95"/>
+      <c r="A351" s="92"/>
       <c r="B351" s="71" t="s">
         <v>788</v>
       </c>
@@ -23857,7 +23862,7 @@
       </c>
     </row>
     <row r="352" spans="1:22" ht="94.2" hidden="1" customHeight="1">
-      <c r="A352" s="95">
+      <c r="A352" s="92">
         <v>93</v>
       </c>
       <c r="B352" s="71" t="s">
@@ -23915,7 +23920,7 @@
       </c>
     </row>
     <row r="353" spans="1:21" ht="94.2" hidden="1" customHeight="1">
-      <c r="A353" s="95"/>
+      <c r="A353" s="92"/>
       <c r="B353" s="71" t="s">
         <v>793</v>
       </c>
@@ -23968,7 +23973,7 @@
       </c>
     </row>
     <row r="354" spans="1:21" ht="94.2" hidden="1" customHeight="1">
-      <c r="A354" s="95"/>
+      <c r="A354" s="92"/>
       <c r="B354" s="71" t="s">
         <v>793</v>
       </c>
@@ -24024,7 +24029,7 @@
       </c>
     </row>
     <row r="355" spans="1:21" ht="46.95" hidden="1" customHeight="1">
-      <c r="A355" s="95"/>
+      <c r="A355" s="92"/>
       <c r="B355" s="71" t="s">
         <v>793</v>
       </c>
@@ -24084,7 +24089,7 @@
       </c>
     </row>
     <row r="356" spans="1:21" ht="13.8" hidden="1">
-      <c r="A356" s="95"/>
+      <c r="A356" s="92"/>
       <c r="B356" s="71" t="s">
         <v>793</v>
       </c>
@@ -24138,7 +24143,7 @@
       </c>
     </row>
     <row r="357" spans="1:21" ht="13.8" hidden="1">
-      <c r="A357" s="95"/>
+      <c r="A357" s="92"/>
       <c r="B357" s="71" t="s">
         <v>793</v>
       </c>
@@ -24471,7 +24476,7 @@
       </c>
     </row>
     <row r="363" spans="1:21" ht="13.8" hidden="1">
-      <c r="A363" s="95"/>
+      <c r="A363" s="92"/>
       <c r="B363" s="71" t="s">
         <v>813</v>
       </c>
@@ -24526,7 +24531,7 @@
       <c r="U363" s="71"/>
     </row>
     <row r="364" spans="1:21" ht="13.8" hidden="1">
-      <c r="A364" s="95"/>
+      <c r="A364" s="92"/>
       <c r="B364" s="71" t="s">
         <v>813</v>
       </c>
@@ -24748,7 +24753,7 @@
       <c r="U367" s="71"/>
     </row>
     <row r="368" spans="1:21" ht="27.6" hidden="1">
-      <c r="A368" s="101">
+      <c r="A368" s="98">
         <v>97</v>
       </c>
       <c r="B368" s="71" t="s">
@@ -24799,7 +24804,7 @@
       </c>
     </row>
     <row r="369" spans="1:21" ht="41.4" hidden="1">
-      <c r="A369" s="106"/>
+      <c r="A369" s="93"/>
       <c r="B369" s="71" t="s">
         <v>820</v>
       </c>
@@ -24859,7 +24864,7 @@
       </c>
     </row>
     <row r="370" spans="1:21" ht="27.6" hidden="1">
-      <c r="A370" s="106"/>
+      <c r="A370" s="93"/>
       <c r="B370" s="71" t="s">
         <v>820</v>
       </c>
@@ -24912,7 +24917,7 @@
       </c>
     </row>
     <row r="371" spans="1:21" ht="27.6" hidden="1">
-      <c r="A371" s="106"/>
+      <c r="A371" s="93"/>
       <c r="B371" s="71" t="s">
         <v>820</v>
       </c>
@@ -24968,7 +24973,7 @@
       </c>
     </row>
     <row r="372" spans="1:21" ht="27.6" hidden="1">
-      <c r="A372" s="102"/>
+      <c r="A372" s="94"/>
       <c r="B372" s="71" t="s">
         <v>820</v>
       </c>
@@ -25023,7 +25028,7 @@
       <c r="U372" s="71"/>
     </row>
     <row r="373" spans="1:21" ht="148.94999999999999" hidden="1" customHeight="1">
-      <c r="A373" s="95">
+      <c r="A373" s="92">
         <v>98</v>
       </c>
       <c r="B373" s="71" t="s">
@@ -25078,7 +25083,7 @@
       </c>
     </row>
     <row r="374" spans="1:21" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A374" s="95"/>
+      <c r="A374" s="92"/>
       <c r="B374" s="71" t="s">
         <v>826</v>
       </c>
@@ -25131,7 +25136,7 @@
       </c>
     </row>
     <row r="375" spans="1:21" ht="34.950000000000003" hidden="1" customHeight="1">
-      <c r="A375" s="95"/>
+      <c r="A375" s="92"/>
       <c r="B375" s="71" t="s">
         <v>826</v>
       </c>
@@ -25184,7 +25189,7 @@
       </c>
     </row>
     <row r="376" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A376" s="95"/>
+      <c r="A376" s="92"/>
       <c r="B376" s="71" t="s">
         <v>826</v>
       </c>
@@ -25237,7 +25242,7 @@
       </c>
     </row>
     <row r="377" spans="1:21" ht="122.4" hidden="1" customHeight="1">
-      <c r="A377" s="95"/>
+      <c r="A377" s="92"/>
       <c r="B377" s="71" t="s">
         <v>826</v>
       </c>
@@ -25280,7 +25285,7 @@
       </c>
     </row>
     <row r="378" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A378" s="95"/>
+      <c r="A378" s="92"/>
       <c r="B378" s="71" t="s">
         <v>826</v>
       </c>
@@ -25332,7 +25337,7 @@
       </c>
     </row>
     <row r="379" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A379" s="95"/>
+      <c r="A379" s="92"/>
       <c r="B379" s="71" t="s">
         <v>826</v>
       </c>
@@ -25384,7 +25389,7 @@
       </c>
     </row>
     <row r="380" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A380" s="95"/>
+      <c r="A380" s="92"/>
       <c r="B380" s="71" t="s">
         <v>826</v>
       </c>
@@ -25430,7 +25435,7 @@
       </c>
     </row>
     <row r="381" spans="1:21" ht="13.8" hidden="1">
-      <c r="A381" s="95"/>
+      <c r="A381" s="92"/>
       <c r="B381" s="71" t="s">
         <v>826</v>
       </c>
@@ -25479,7 +25484,7 @@
       <c r="U381" s="71"/>
     </row>
     <row r="382" spans="1:21" ht="13.8" hidden="1">
-      <c r="A382" s="95"/>
+      <c r="A382" s="92"/>
       <c r="B382" s="71" t="s">
         <v>826</v>
       </c>
@@ -25533,7 +25538,7 @@
       <c r="U382" s="71"/>
     </row>
     <row r="383" spans="1:21" ht="13.8" hidden="1">
-      <c r="A383" s="95"/>
+      <c r="A383" s="92"/>
       <c r="B383" s="71" t="s">
         <v>826</v>
       </c>
@@ -25585,7 +25590,7 @@
       </c>
     </row>
     <row r="384" spans="1:21" ht="13.8" hidden="1">
-      <c r="A384" s="95"/>
+      <c r="A384" s="92"/>
       <c r="B384" s="71" t="s">
         <v>826</v>
       </c>
@@ -25639,7 +25644,7 @@
       <c r="U384" s="71"/>
     </row>
     <row r="385" spans="1:21" ht="27.6" hidden="1">
-      <c r="A385" s="102">
+      <c r="A385" s="94">
         <v>99</v>
       </c>
       <c r="B385" s="71" t="s">
@@ -25694,7 +25699,7 @@
       </c>
     </row>
     <row r="386" spans="1:21" ht="163.19999999999999" hidden="1" customHeight="1">
-      <c r="A386" s="95"/>
+      <c r="A386" s="92"/>
       <c r="B386" s="71" t="s">
         <v>854</v>
       </c>
@@ -25747,7 +25752,7 @@
       </c>
     </row>
     <row r="387" spans="1:21" ht="61.2" hidden="1" customHeight="1">
-      <c r="A387" s="95"/>
+      <c r="A387" s="92"/>
       <c r="B387" s="71" t="s">
         <v>854</v>
       </c>
@@ -25803,7 +25808,7 @@
       <c r="U387" s="71"/>
     </row>
     <row r="388" spans="1:21" ht="13.8" hidden="1">
-      <c r="A388" s="95"/>
+      <c r="A388" s="92"/>
       <c r="B388" s="71" t="s">
         <v>854</v>
       </c>
@@ -25857,7 +25862,7 @@
       </c>
     </row>
     <row r="389" spans="1:21" ht="13.8" hidden="1">
-      <c r="A389" s="95"/>
+      <c r="A389" s="92"/>
       <c r="B389" s="71" t="s">
         <v>853</v>
       </c>
@@ -25911,7 +25916,7 @@
       </c>
     </row>
     <row r="390" spans="1:21" ht="13.8" hidden="1">
-      <c r="A390" s="95"/>
+      <c r="A390" s="92"/>
       <c r="B390" s="71" t="s">
         <v>853</v>
       </c>
@@ -25967,7 +25972,7 @@
       </c>
     </row>
     <row r="391" spans="1:21" ht="13.8" hidden="1">
-      <c r="A391" s="95"/>
+      <c r="A391" s="92"/>
       <c r="B391" s="71" t="s">
         <v>853</v>
       </c>
@@ -26008,7 +26013,7 @@
       </c>
     </row>
     <row r="392" spans="1:21" ht="13.8" hidden="1">
-      <c r="A392" s="95"/>
+      <c r="A392" s="92"/>
       <c r="B392" s="66" t="s">
         <v>853</v>
       </c>
@@ -26115,7 +26120,7 @@
       </c>
     </row>
     <row r="394" spans="1:21" ht="58.2" hidden="1" customHeight="1">
-      <c r="A394" s="95">
+      <c r="A394" s="92">
         <v>100</v>
       </c>
       <c r="B394" s="66" t="s">
@@ -26170,7 +26175,7 @@
       </c>
     </row>
     <row r="395" spans="1:21" ht="41.4" hidden="1">
-      <c r="A395" s="95"/>
+      <c r="A395" s="92"/>
       <c r="B395" s="66" t="s">
         <v>863</v>
       </c>
@@ -26223,7 +26228,7 @@
       </c>
     </row>
     <row r="396" spans="1:21" ht="18" hidden="1" customHeight="1">
-      <c r="A396" s="95"/>
+      <c r="A396" s="92"/>
       <c r="B396" s="71" t="s">
         <v>863</v>
       </c>
@@ -26279,7 +26284,7 @@
       </c>
     </row>
     <row r="397" spans="1:21" ht="27.6" hidden="1">
-      <c r="A397" s="95"/>
+      <c r="A397" s="92"/>
       <c r="B397" s="71" t="s">
         <v>863</v>
       </c>
@@ -26331,7 +26336,7 @@
       </c>
     </row>
     <row r="398" spans="1:21" ht="18" hidden="1" customHeight="1">
-      <c r="A398" s="95"/>
+      <c r="A398" s="92"/>
       <c r="B398" s="71" t="s">
         <v>863</v>
       </c>
@@ -26385,7 +26390,7 @@
       <c r="U398" s="71"/>
     </row>
     <row r="399" spans="1:21" ht="13.8" hidden="1">
-      <c r="A399" s="95"/>
+      <c r="A399" s="92"/>
       <c r="B399" s="71" t="s">
         <v>863</v>
       </c>
@@ -26439,7 +26444,7 @@
       <c r="U399" s="71"/>
     </row>
     <row r="400" spans="1:21" ht="27.6" hidden="1">
-      <c r="A400" s="110">
+      <c r="A400" s="102">
         <v>101</v>
       </c>
       <c r="B400" s="71" t="s">
@@ -26496,7 +26501,7 @@
       </c>
     </row>
     <row r="401" spans="1:21" ht="31.95" hidden="1" customHeight="1">
-      <c r="A401" s="110"/>
+      <c r="A401" s="102"/>
       <c r="B401" s="71" t="s">
         <v>873</v>
       </c>
@@ -26537,7 +26542,7 @@
       <c r="U401" s="66"/>
     </row>
     <row r="402" spans="1:21" ht="31.95" hidden="1" customHeight="1">
-      <c r="A402" s="110"/>
+      <c r="A402" s="102"/>
       <c r="B402" s="71" t="s">
         <v>873</v>
       </c>
@@ -26591,7 +26596,7 @@
       </c>
     </row>
     <row r="403" spans="1:21" ht="31.95" hidden="1" customHeight="1">
-      <c r="A403" s="110"/>
+      <c r="A403" s="102"/>
       <c r="B403" s="71" t="s">
         <v>873</v>
       </c>
@@ -26647,7 +26652,7 @@
       </c>
     </row>
     <row r="404" spans="1:21" ht="31.95" hidden="1" customHeight="1">
-      <c r="A404" s="110"/>
+      <c r="A404" s="102"/>
       <c r="B404" s="71" t="s">
         <v>873</v>
       </c>
@@ -26701,7 +26706,7 @@
       <c r="U404" s="71"/>
     </row>
     <row r="405" spans="1:21" ht="13.8" hidden="1">
-      <c r="A405" s="110"/>
+      <c r="A405" s="102"/>
       <c r="B405" s="71" t="s">
         <v>873</v>
       </c>
@@ -26757,7 +26762,7 @@
       </c>
     </row>
     <row r="406" spans="1:21" ht="36" hidden="1" customHeight="1">
-      <c r="A406" s="95">
+      <c r="A406" s="92">
         <v>102</v>
       </c>
       <c r="B406" s="66" t="s">
@@ -26812,7 +26817,7 @@
       </c>
     </row>
     <row r="407" spans="1:21" ht="13.8" hidden="1">
-      <c r="A407" s="95"/>
+      <c r="A407" s="92"/>
       <c r="B407" s="71" t="s">
         <v>880</v>
       </c>
@@ -26868,7 +26873,7 @@
       </c>
     </row>
     <row r="408" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A408" s="95">
+      <c r="A408" s="92">
         <v>103</v>
       </c>
       <c r="B408" s="71" t="s">
@@ -26924,7 +26929,7 @@
       </c>
     </row>
     <row r="409" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A409" s="95"/>
+      <c r="A409" s="92"/>
       <c r="B409" s="71" t="s">
         <v>884</v>
       </c>
@@ -26980,7 +26985,7 @@
       </c>
     </row>
     <row r="410" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A410" s="95"/>
+      <c r="A410" s="92"/>
       <c r="B410" s="71" t="s">
         <v>884</v>
       </c>
@@ -27035,7 +27040,7 @@
       </c>
     </row>
     <row r="411" spans="1:21" ht="13.8" hidden="1">
-      <c r="A411" s="95"/>
+      <c r="A411" s="92"/>
       <c r="B411" s="71" t="s">
         <v>884</v>
       </c>
@@ -27091,7 +27096,7 @@
       </c>
     </row>
     <row r="412" spans="1:21" ht="60" hidden="1" customHeight="1">
-      <c r="A412" s="95">
+      <c r="A412" s="92">
         <v>104</v>
       </c>
       <c r="B412" s="71" t="s">
@@ -27146,7 +27151,7 @@
       </c>
     </row>
     <row r="413" spans="1:21" ht="60" hidden="1" customHeight="1">
-      <c r="A413" s="95"/>
+      <c r="A413" s="92"/>
       <c r="B413" s="71" t="s">
         <v>889</v>
       </c>
@@ -27206,7 +27211,7 @@
       </c>
     </row>
     <row r="414" spans="1:21" ht="60" hidden="1" customHeight="1">
-      <c r="A414" s="95"/>
+      <c r="A414" s="92"/>
       <c r="B414" s="71"/>
       <c r="C414" s="66"/>
       <c r="D414" s="66"/>
@@ -27229,7 +27234,7 @@
       <c r="U414" s="71"/>
     </row>
     <row r="415" spans="1:21" ht="55.2" hidden="1">
-      <c r="A415" s="95"/>
+      <c r="A415" s="92"/>
       <c r="B415" s="71" t="s">
         <v>889</v>
       </c>
@@ -27282,7 +27287,7 @@
       </c>
     </row>
     <row r="416" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A416" s="95"/>
+      <c r="A416" s="92"/>
       <c r="B416" s="71" t="s">
         <v>889</v>
       </c>
@@ -27337,7 +27342,7 @@
       </c>
     </row>
     <row r="417" spans="1:21" ht="41.4" hidden="1">
-      <c r="A417" s="95">
+      <c r="A417" s="92">
         <v>105</v>
       </c>
       <c r="B417" s="71" t="s">
@@ -27392,7 +27397,7 @@
       </c>
     </row>
     <row r="418" spans="1:21" ht="142.94999999999999" hidden="1" customHeight="1">
-      <c r="A418" s="95"/>
+      <c r="A418" s="92"/>
       <c r="B418" s="71" t="s">
         <v>896</v>
       </c>
@@ -27439,7 +27444,7 @@
       </c>
     </row>
     <row r="419" spans="1:21" ht="13.8" hidden="1">
-      <c r="A419" s="95"/>
+      <c r="A419" s="92"/>
       <c r="B419" s="71" t="s">
         <v>896</v>
       </c>
@@ -27495,7 +27500,7 @@
       </c>
     </row>
     <row r="420" spans="1:21" ht="13.8" hidden="1">
-      <c r="A420" s="95"/>
+      <c r="A420" s="92"/>
       <c r="B420" s="71" t="s">
         <v>896</v>
       </c>
@@ -27551,7 +27556,7 @@
       </c>
     </row>
     <row r="421" spans="1:21" ht="13.8" hidden="1">
-      <c r="A421" s="95"/>
+      <c r="A421" s="92"/>
       <c r="B421" s="71" t="s">
         <v>896</v>
       </c>
@@ -27607,7 +27612,7 @@
       </c>
     </row>
     <row r="422" spans="1:21" ht="27.6" hidden="1">
-      <c r="A422" s="95"/>
+      <c r="A422" s="92"/>
       <c r="B422" s="71" t="s">
         <v>896</v>
       </c>
@@ -27650,7 +27655,7 @@
       </c>
     </row>
     <row r="423" spans="1:21" ht="13.8" hidden="1">
-      <c r="A423" s="95"/>
+      <c r="A423" s="92"/>
       <c r="B423" s="71" t="s">
         <v>896</v>
       </c>
@@ -27700,7 +27705,7 @@
       </c>
     </row>
     <row r="424" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A424" s="95"/>
+      <c r="A424" s="92"/>
       <c r="B424" s="71" t="s">
         <v>896</v>
       </c>
@@ -27856,7 +27861,7 @@
       </c>
     </row>
     <row r="427" spans="1:21" ht="27.6" hidden="1">
-      <c r="A427" s="95">
+      <c r="A427" s="92">
         <v>107</v>
       </c>
       <c r="B427" s="71" t="s">
@@ -27913,7 +27918,7 @@
       </c>
     </row>
     <row r="428" spans="1:21" ht="13.8" hidden="1">
-      <c r="A428" s="95"/>
+      <c r="A428" s="92"/>
       <c r="B428" s="71" t="s">
         <v>913</v>
       </c>
@@ -27967,7 +27972,7 @@
       <c r="U428" s="71"/>
     </row>
     <row r="429" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A429" s="95"/>
+      <c r="A429" s="92"/>
       <c r="B429" s="71" t="s">
         <v>913</v>
       </c>
@@ -28019,7 +28024,7 @@
       </c>
     </row>
     <row r="430" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A430" s="95"/>
+      <c r="A430" s="92"/>
       <c r="B430" s="71" t="s">
         <v>912</v>
       </c>
@@ -28071,7 +28076,7 @@
       </c>
     </row>
     <row r="431" spans="1:21" ht="40.950000000000003" hidden="1" customHeight="1">
-      <c r="A431" s="95"/>
+      <c r="A431" s="92"/>
       <c r="B431" s="71" t="s">
         <v>912</v>
       </c>
@@ -28123,7 +28128,7 @@
       </c>
     </row>
     <row r="432" spans="1:21" ht="13.8" hidden="1">
-      <c r="A432" s="95"/>
+      <c r="A432" s="92"/>
       <c r="B432" s="71" t="s">
         <v>913</v>
       </c>
@@ -28177,7 +28182,7 @@
       <c r="U432" s="71"/>
     </row>
     <row r="433" spans="1:21" ht="13.8" hidden="1">
-      <c r="A433" s="95"/>
+      <c r="A433" s="92"/>
       <c r="B433" s="71" t="s">
         <v>912</v>
       </c>
@@ -28231,7 +28236,7 @@
       <c r="U433" s="66"/>
     </row>
     <row r="434" spans="1:21" ht="13.8" hidden="1">
-      <c r="A434" s="106"/>
+      <c r="A434" s="93"/>
       <c r="B434" s="71" t="s">
         <v>924</v>
       </c>
@@ -28253,37 +28258,37 @@
       </c>
       <c r="I434" s="71"/>
       <c r="J434" s="71"/>
-      <c r="K434" s="99">
+      <c r="K434" s="95">
         <v>12746524997</v>
       </c>
-      <c r="L434" s="99">
+      <c r="L434" s="95">
         <v>1000000000</v>
       </c>
-      <c r="M434" s="99">
+      <c r="M434" s="95">
         <f>+K434+L434</f>
         <v>13746524997</v>
       </c>
-      <c r="N434" s="96" t="s">
+      <c r="N434" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="O434" s="96" t="s">
+      <c r="O434" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="P434" s="95">
+      <c r="P434" s="92">
         <v>2025</v>
       </c>
       <c r="Q434" s="66"/>
       <c r="R434" s="66"/>
       <c r="S434" s="66"/>
-      <c r="T434" s="113">
+      <c r="T434" s="96">
         <v>0.65</v>
       </c>
-      <c r="U434" s="95" t="s">
+      <c r="U434" s="92" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="435" spans="1:21" ht="27.6" hidden="1">
-      <c r="A435" s="106"/>
+      <c r="A435" s="93"/>
       <c r="B435" s="71" t="s">
         <v>924</v>
       </c>
@@ -28305,20 +28310,20 @@
       </c>
       <c r="I435" s="71"/>
       <c r="J435" s="71"/>
-      <c r="K435" s="99"/>
-      <c r="L435" s="99"/>
-      <c r="M435" s="99"/>
-      <c r="N435" s="96"/>
-      <c r="O435" s="96"/>
-      <c r="P435" s="95"/>
+      <c r="K435" s="95"/>
+      <c r="L435" s="95"/>
+      <c r="M435" s="95"/>
+      <c r="N435" s="97"/>
+      <c r="O435" s="97"/>
+      <c r="P435" s="92"/>
       <c r="Q435" s="66"/>
       <c r="R435" s="66"/>
       <c r="S435" s="66"/>
-      <c r="T435" s="113"/>
-      <c r="U435" s="95"/>
+      <c r="T435" s="96"/>
+      <c r="U435" s="92"/>
     </row>
     <row r="436" spans="1:21" ht="13.8" hidden="1">
-      <c r="A436" s="106"/>
+      <c r="A436" s="93"/>
       <c r="B436" s="71" t="s">
         <v>924</v>
       </c>
@@ -28372,7 +28377,7 @@
       </c>
     </row>
     <row r="437" spans="1:21" ht="13.8" hidden="1">
-      <c r="A437" s="106"/>
+      <c r="A437" s="93"/>
       <c r="B437" s="71" t="s">
         <v>928</v>
       </c>
@@ -28426,7 +28431,7 @@
       </c>
     </row>
     <row r="438" spans="1:21" ht="13.8" hidden="1">
-      <c r="A438" s="106"/>
+      <c r="A438" s="93"/>
       <c r="B438" s="71" t="s">
         <v>924</v>
       </c>
@@ -28478,7 +28483,7 @@
       </c>
     </row>
     <row r="439" spans="1:21" ht="27.6" hidden="1">
-      <c r="A439" s="102"/>
+      <c r="A439" s="94"/>
       <c r="B439" s="71" t="s">
         <v>924</v>
       </c>
@@ -28531,7 +28536,7 @@
       </c>
     </row>
     <row r="440" spans="1:21" ht="57" hidden="1" customHeight="1">
-      <c r="A440" s="101">
+      <c r="A440" s="98">
         <v>109</v>
       </c>
       <c r="B440" s="71" t="s">
@@ -28585,7 +28590,7 @@
       </c>
     </row>
     <row r="441" spans="1:21" ht="57" hidden="1" customHeight="1">
-      <c r="A441" s="106"/>
+      <c r="A441" s="93"/>
       <c r="B441" s="71" t="s">
         <v>936</v>
       </c>
@@ -28636,7 +28641,7 @@
       </c>
     </row>
     <row r="442" spans="1:21" ht="36.6" hidden="1" customHeight="1">
-      <c r="A442" s="106"/>
+      <c r="A442" s="93"/>
       <c r="B442" s="71" t="s">
         <v>936</v>
       </c>
@@ -28691,7 +28696,7 @@
       </c>
     </row>
     <row r="443" spans="1:21" ht="36.6" hidden="1" customHeight="1">
-      <c r="A443" s="106"/>
+      <c r="A443" s="93"/>
       <c r="B443" s="71" t="s">
         <v>936</v>
       </c>
@@ -28745,7 +28750,7 @@
       </c>
     </row>
     <row r="444" spans="1:21" ht="64.95" hidden="1" customHeight="1">
-      <c r="A444" s="106"/>
+      <c r="A444" s="93"/>
       <c r="B444" s="71" t="s">
         <v>936</v>
       </c>
@@ -28797,7 +28802,7 @@
       </c>
     </row>
     <row r="445" spans="1:21" ht="36.6" hidden="1" customHeight="1">
-      <c r="A445" s="106"/>
+      <c r="A445" s="93"/>
       <c r="B445" s="71" t="s">
         <v>936</v>
       </c>
@@ -28847,7 +28852,7 @@
       </c>
     </row>
     <row r="446" spans="1:21" ht="36.6" hidden="1" customHeight="1">
-      <c r="A446" s="106"/>
+      <c r="A446" s="93"/>
       <c r="B446" s="71" t="s">
         <v>936</v>
       </c>
@@ -28884,7 +28889,7 @@
       <c r="U446" s="71"/>
     </row>
     <row r="447" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A447" s="102"/>
+      <c r="A447" s="94"/>
       <c r="B447" s="71" t="s">
         <v>936</v>
       </c>
@@ -28938,7 +28943,7 @@
       <c r="U447" s="44"/>
     </row>
     <row r="448" spans="1:21" ht="27.6" hidden="1">
-      <c r="A448" s="95"/>
+      <c r="A448" s="92"/>
       <c r="B448" s="71" t="s">
         <v>946</v>
       </c>
@@ -28994,7 +28999,7 @@
       </c>
     </row>
     <row r="449" spans="1:21" ht="41.4" hidden="1">
-      <c r="A449" s="95"/>
+      <c r="A449" s="92"/>
       <c r="B449" s="51" t="s">
         <v>946</v>
       </c>
@@ -29054,7 +29059,7 @@
       </c>
     </row>
     <row r="450" spans="1:21" ht="27.6" hidden="1">
-      <c r="A450" s="101">
+      <c r="A450" s="98">
         <v>111</v>
       </c>
       <c r="B450" s="71" t="s">
@@ -29110,7 +29115,7 @@
       </c>
     </row>
     <row r="451" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A451" s="106"/>
+      <c r="A451" s="93"/>
       <c r="B451" s="71" t="s">
         <v>953</v>
       </c>
@@ -29164,7 +29169,7 @@
       </c>
     </row>
     <row r="452" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A452" s="106"/>
+      <c r="A452" s="93"/>
       <c r="B452" s="71" t="s">
         <v>953</v>
       </c>
@@ -29222,7 +29227,7 @@
       </c>
     </row>
     <row r="453" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A453" s="102"/>
+      <c r="A453" s="94"/>
       <c r="B453" s="71" t="s">
         <v>953</v>
       </c>
@@ -29276,7 +29281,7 @@
       </c>
     </row>
     <row r="454" spans="1:21" ht="42.6" hidden="1" customHeight="1">
-      <c r="A454" s="95">
+      <c r="A454" s="92">
         <v>112</v>
       </c>
       <c r="B454" s="71" t="s">
@@ -29337,7 +29342,7 @@
       </c>
     </row>
     <row r="455" spans="1:21" ht="13.8" hidden="1">
-      <c r="A455" s="95"/>
+      <c r="A455" s="92"/>
       <c r="B455" s="71" t="s">
         <v>960</v>
       </c>
@@ -29392,7 +29397,7 @@
       <c r="U455" s="71"/>
     </row>
     <row r="456" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A456" s="95"/>
+      <c r="A456" s="92"/>
       <c r="B456" s="71" t="s">
         <v>960</v>
       </c>
@@ -29449,7 +29454,7 @@
       <c r="U456" s="71"/>
     </row>
     <row r="457" spans="1:21" ht="27.6" hidden="1">
-      <c r="A457" s="95">
+      <c r="A457" s="92">
         <v>113</v>
       </c>
       <c r="B457" s="71" t="s">
@@ -29502,7 +29507,7 @@
       </c>
     </row>
     <row r="458" spans="1:21" ht="13.8" hidden="1">
-      <c r="A458" s="95"/>
+      <c r="A458" s="92"/>
       <c r="B458" s="71" t="s">
         <v>964</v>
       </c>
@@ -29555,7 +29560,7 @@
       </c>
     </row>
     <row r="459" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A459" s="95"/>
+      <c r="A459" s="92"/>
       <c r="B459" s="71" t="s">
         <v>964</v>
       </c>
@@ -29609,7 +29614,7 @@
       <c r="U459" s="66"/>
     </row>
     <row r="460" spans="1:21" ht="37.950000000000003" hidden="1" customHeight="1">
-      <c r="A460" s="95"/>
+      <c r="A460" s="92"/>
       <c r="B460" s="71" t="s">
         <v>964</v>
       </c>
@@ -29657,7 +29662,7 @@
       <c r="U460" s="66"/>
     </row>
     <row r="461" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A461" s="95"/>
+      <c r="A461" s="92"/>
       <c r="B461" s="71" t="s">
         <v>964</v>
       </c>
@@ -30038,7 +30043,7 @@
       </c>
     </row>
     <row r="468" spans="1:21" ht="33.6" hidden="1" customHeight="1">
-      <c r="A468" s="106"/>
+      <c r="A468" s="93"/>
       <c r="B468" s="71" t="s">
         <v>981</v>
       </c>
@@ -30089,7 +30094,7 @@
       </c>
     </row>
     <row r="469" spans="1:21" ht="33.6" hidden="1" customHeight="1">
-      <c r="A469" s="106"/>
+      <c r="A469" s="93"/>
       <c r="B469" s="71" t="s">
         <v>325</v>
       </c>
@@ -30143,7 +30148,7 @@
       <c r="U469" s="71"/>
     </row>
     <row r="470" spans="1:21" ht="33.6" hidden="1" customHeight="1">
-      <c r="A470" s="106"/>
+      <c r="A470" s="93"/>
       <c r="B470" s="71" t="s">
         <v>325</v>
       </c>
@@ -30197,7 +30202,7 @@
       <c r="U470" s="71"/>
     </row>
     <row r="471" spans="1:21" ht="33.6" hidden="1" customHeight="1">
-      <c r="A471" s="106"/>
+      <c r="A471" s="93"/>
       <c r="B471" s="71" t="s">
         <v>325</v>
       </c>
@@ -30251,7 +30256,7 @@
       <c r="U471" s="71"/>
     </row>
     <row r="472" spans="1:21" ht="33.6" hidden="1" customHeight="1">
-      <c r="A472" s="106"/>
+      <c r="A472" s="93"/>
       <c r="B472" s="71" t="s">
         <v>325</v>
       </c>
@@ -30307,7 +30312,7 @@
       </c>
     </row>
     <row r="473" spans="1:21" ht="33.6" hidden="1" customHeight="1">
-      <c r="A473" s="106"/>
+      <c r="A473" s="93"/>
       <c r="B473" s="71" t="s">
         <v>325</v>
       </c>
@@ -30359,7 +30364,7 @@
       </c>
     </row>
     <row r="474" spans="1:21" ht="39" hidden="1" customHeight="1">
-      <c r="A474" s="102"/>
+      <c r="A474" s="94"/>
       <c r="B474" s="71" t="s">
         <v>981</v>
       </c>
@@ -30409,7 +30414,7 @@
       </c>
     </row>
     <row r="475" spans="1:21" ht="39" hidden="1" customHeight="1">
-      <c r="A475" s="95">
+      <c r="A475" s="92">
         <v>116</v>
       </c>
       <c r="B475" s="71" t="s">
@@ -30421,7 +30426,7 @@
       <c r="D475" s="66" t="s">
         <v>174</v>
       </c>
-      <c r="E475" s="98">
+      <c r="E475" s="112">
         <v>2025003050036</v>
       </c>
       <c r="F475" s="71" t="s">
@@ -30435,14 +30440,14 @@
       </c>
       <c r="I475" s="71"/>
       <c r="J475" s="71"/>
-      <c r="K475" s="100">
+      <c r="K475" s="113">
         <f>+M475</f>
         <v>14202451801</v>
       </c>
-      <c r="L475" s="100">
+      <c r="L475" s="113">
         <v>0</v>
       </c>
-      <c r="M475" s="99">
+      <c r="M475" s="95">
         <v>14202451801</v>
       </c>
       <c r="N475" s="71" t="s">
@@ -30460,12 +30465,12 @@
       <c r="R475" s="66"/>
       <c r="S475" s="66"/>
       <c r="T475" s="71"/>
-      <c r="U475" s="96" t="s">
+      <c r="U475" s="97" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="476" spans="1:21" ht="39" hidden="1" customHeight="1">
-      <c r="A476" s="95"/>
+      <c r="A476" s="92"/>
       <c r="B476" s="71" t="s">
         <v>993</v>
       </c>
@@ -30475,7 +30480,7 @@
       <c r="D476" s="66" t="s">
         <v>174</v>
       </c>
-      <c r="E476" s="98"/>
+      <c r="E476" s="112"/>
       <c r="F476" s="71" t="s">
         <v>175</v>
       </c>
@@ -30487,9 +30492,9 @@
       </c>
       <c r="I476" s="71"/>
       <c r="J476" s="71"/>
-      <c r="K476" s="100"/>
-      <c r="L476" s="100"/>
-      <c r="M476" s="99"/>
+      <c r="K476" s="113"/>
+      <c r="L476" s="113"/>
+      <c r="M476" s="95"/>
       <c r="N476" s="71" t="s">
         <v>36</v>
       </c>
@@ -30505,10 +30510,10 @@
       <c r="R476" s="66"/>
       <c r="S476" s="66"/>
       <c r="T476" s="71"/>
-      <c r="U476" s="96"/>
+      <c r="U476" s="97"/>
     </row>
     <row r="477" spans="1:21" ht="39" hidden="1" customHeight="1">
-      <c r="A477" s="95"/>
+      <c r="A477" s="92"/>
       <c r="B477" s="71" t="s">
         <v>993</v>
       </c>
@@ -30566,7 +30571,7 @@
       </c>
     </row>
     <row r="478" spans="1:21" ht="36" hidden="1" customHeight="1">
-      <c r="A478" s="95"/>
+      <c r="A478" s="92"/>
       <c r="B478" s="71" t="s">
         <v>993</v>
       </c>
@@ -31001,7 +31006,7 @@
       <c r="U485" s="66"/>
     </row>
     <row r="486" spans="1:21" ht="35.25" hidden="1" customHeight="1">
-      <c r="A486" s="95">
+      <c r="A486" s="92">
         <v>121</v>
       </c>
       <c r="B486" s="71" t="s">
@@ -31057,7 +31062,7 @@
       <c r="U486" s="71"/>
     </row>
     <row r="487" spans="1:21" ht="36" hidden="1" customHeight="1">
-      <c r="A487" s="95"/>
+      <c r="A487" s="92"/>
       <c r="B487" s="71" t="s">
         <v>1009</v>
       </c>
@@ -31109,7 +31114,7 @@
       </c>
     </row>
     <row r="488" spans="1:21" ht="96.6" hidden="1">
-      <c r="A488" s="95"/>
+      <c r="A488" s="92"/>
       <c r="B488" s="71" t="s">
         <v>1009</v>
       </c>
@@ -31273,7 +31278,7 @@
       <c r="U490" s="71"/>
     </row>
     <row r="491" spans="1:21" ht="13.8" hidden="1">
-      <c r="A491" s="106"/>
+      <c r="A491" s="93"/>
       <c r="B491" s="71" t="s">
         <v>1019</v>
       </c>
@@ -31327,7 +31332,7 @@
       <c r="U491" s="71"/>
     </row>
     <row r="492" spans="1:21" ht="13.8" hidden="1">
-      <c r="A492" s="106"/>
+      <c r="A492" s="93"/>
       <c r="B492" s="71" t="s">
         <v>1019</v>
       </c>
@@ -31381,7 +31386,7 @@
       <c r="U492" s="71"/>
     </row>
     <row r="493" spans="1:21" ht="55.2" hidden="1">
-      <c r="A493" s="106"/>
+      <c r="A493" s="93"/>
       <c r="B493" s="71" t="s">
         <v>1019</v>
       </c>
@@ -31432,7 +31437,7 @@
       </c>
     </row>
     <row r="494" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A494" s="102"/>
+      <c r="A494" s="94"/>
       <c r="B494" s="71" t="s">
         <v>1019</v>
       </c>
@@ -31486,7 +31491,7 @@
       <c r="U494" s="71"/>
     </row>
     <row r="495" spans="1:21" ht="15" hidden="1" customHeight="1">
-      <c r="A495" s="95">
+      <c r="A495" s="92">
         <v>124</v>
       </c>
       <c r="B495" s="71" t="s">
@@ -31544,7 +31549,7 @@
       </c>
     </row>
     <row r="496" spans="1:21" ht="27.6" hidden="1">
-      <c r="A496" s="95"/>
+      <c r="A496" s="92"/>
       <c r="B496" s="71" t="s">
         <v>1026</v>
       </c>
@@ -31596,7 +31601,7 @@
       </c>
     </row>
     <row r="497" spans="1:21" ht="13.8" hidden="1">
-      <c r="A497" s="95"/>
+      <c r="A497" s="92"/>
       <c r="B497" s="71" t="s">
         <v>1026</v>
       </c>
@@ -31650,7 +31655,7 @@
       </c>
     </row>
     <row r="498" spans="1:21" ht="40.200000000000003" hidden="1" customHeight="1">
-      <c r="A498" s="95"/>
+      <c r="A498" s="92"/>
       <c r="B498" s="71" t="s">
         <v>1032</v>
       </c>
@@ -31765,7 +31770,7 @@
       </c>
     </row>
     <row r="500" spans="1:21" ht="27.6" hidden="1">
-      <c r="A500" s="96">
+      <c r="A500" s="97">
         <v>126</v>
       </c>
       <c r="B500" s="71" t="s">
@@ -31826,7 +31831,7 @@
       </c>
     </row>
     <row r="501" spans="1:21" ht="13.8" hidden="1">
-      <c r="A501" s="96"/>
+      <c r="A501" s="97"/>
       <c r="B501" s="71" t="s">
         <v>1033</v>
       </c>
@@ -31877,7 +31882,7 @@
       <c r="U501" s="71"/>
     </row>
     <row r="502" spans="1:21" ht="78" hidden="1" customHeight="1">
-      <c r="A502" s="96"/>
+      <c r="A502" s="97"/>
       <c r="B502" s="71" t="s">
         <v>1033</v>
       </c>
@@ -31933,7 +31938,7 @@
       </c>
     </row>
     <row r="503" spans="1:21" ht="41.4" hidden="1">
-      <c r="A503" s="95">
+      <c r="A503" s="92">
         <v>127</v>
       </c>
       <c r="B503" s="71" t="s">
@@ -31995,7 +32000,7 @@
       </c>
     </row>
     <row r="504" spans="1:21" ht="13.8" hidden="1">
-      <c r="A504" s="95"/>
+      <c r="A504" s="92"/>
       <c r="B504" s="71" t="s">
         <v>1041</v>
       </c>
@@ -32053,7 +32058,7 @@
       <c r="U504" s="71"/>
     </row>
     <row r="505" spans="1:21" ht="55.2" hidden="1">
-      <c r="A505" s="95"/>
+      <c r="A505" s="92"/>
       <c r="B505" s="51" t="s">
         <v>1041</v>
       </c>
@@ -32193,18 +32198,107 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="137">
-    <mergeCell ref="A408:A411"/>
-    <mergeCell ref="A412:A416"/>
-    <mergeCell ref="A417:A424"/>
-    <mergeCell ref="A427:A433"/>
-    <mergeCell ref="A434:A439"/>
-    <mergeCell ref="K434:K435"/>
-    <mergeCell ref="T434:T435"/>
-    <mergeCell ref="L434:L435"/>
-    <mergeCell ref="M434:M435"/>
-    <mergeCell ref="N434:N435"/>
-    <mergeCell ref="O434:O435"/>
-    <mergeCell ref="P434:P435"/>
+    <mergeCell ref="M91:M101"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="Q91:Q92"/>
+    <mergeCell ref="T91:T92"/>
+    <mergeCell ref="E475:E476"/>
+    <mergeCell ref="U91:U92"/>
+    <mergeCell ref="M475:M476"/>
+    <mergeCell ref="K475:K476"/>
+    <mergeCell ref="L475:L476"/>
+    <mergeCell ref="U475:U476"/>
+    <mergeCell ref="U434:U435"/>
+    <mergeCell ref="H310:H311"/>
+    <mergeCell ref="H312:H313"/>
+    <mergeCell ref="J310:J311"/>
+    <mergeCell ref="I310:I311"/>
+    <mergeCell ref="I312:I313"/>
+    <mergeCell ref="J312:J313"/>
+    <mergeCell ref="E312:E313"/>
+    <mergeCell ref="K91:K101"/>
+    <mergeCell ref="L91:L101"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="A78:A117"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A169:A173"/>
+    <mergeCell ref="A174:A180"/>
+    <mergeCell ref="A183:A185"/>
+    <mergeCell ref="A187:A189"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A121:A124"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="A138:A144"/>
+    <mergeCell ref="A145:A147"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A153:A164"/>
+    <mergeCell ref="A214:A218"/>
+    <mergeCell ref="A223:A228"/>
+    <mergeCell ref="A235:A240"/>
+    <mergeCell ref="A241:A247"/>
+    <mergeCell ref="A249:A251"/>
+    <mergeCell ref="A255:A260"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="A197:A200"/>
+    <mergeCell ref="A204:A206"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="A295:A297"/>
+    <mergeCell ref="A298:A300"/>
+    <mergeCell ref="A301:A302"/>
+    <mergeCell ref="A303:A304"/>
+    <mergeCell ref="A305:A308"/>
+    <mergeCell ref="F310:F311"/>
+    <mergeCell ref="A261:A265"/>
+    <mergeCell ref="A267:A270"/>
+    <mergeCell ref="A272:A276"/>
+    <mergeCell ref="A281:A282"/>
+    <mergeCell ref="A283:A284"/>
+    <mergeCell ref="A285:A293"/>
+    <mergeCell ref="E310:E311"/>
+    <mergeCell ref="A400:A405"/>
+    <mergeCell ref="A406:A407"/>
+    <mergeCell ref="P310:P311"/>
+    <mergeCell ref="U310:U311"/>
+    <mergeCell ref="T310:T311"/>
+    <mergeCell ref="A311:A316"/>
+    <mergeCell ref="F312:F313"/>
+    <mergeCell ref="G312:G313"/>
+    <mergeCell ref="K312:K313"/>
+    <mergeCell ref="L312:L313"/>
+    <mergeCell ref="M312:M313"/>
+    <mergeCell ref="N312:N313"/>
+    <mergeCell ref="G310:G311"/>
+    <mergeCell ref="K310:K311"/>
+    <mergeCell ref="L310:L311"/>
+    <mergeCell ref="M310:M311"/>
+    <mergeCell ref="N310:N311"/>
+    <mergeCell ref="O310:O311"/>
+    <mergeCell ref="Q310:Q311"/>
+    <mergeCell ref="Q312:Q313"/>
+    <mergeCell ref="O312:O313"/>
+    <mergeCell ref="P312:P313"/>
+    <mergeCell ref="U312:U313"/>
+    <mergeCell ref="T312:T313"/>
     <mergeCell ref="A319:A320"/>
     <mergeCell ref="A321:A330"/>
     <mergeCell ref="A335:A338"/>
@@ -32229,107 +32323,18 @@
     <mergeCell ref="A373:A384"/>
     <mergeCell ref="A385:A392"/>
     <mergeCell ref="A394:A399"/>
-    <mergeCell ref="A400:A405"/>
-    <mergeCell ref="A406:A407"/>
-    <mergeCell ref="P310:P311"/>
-    <mergeCell ref="U310:U311"/>
-    <mergeCell ref="T310:T311"/>
-    <mergeCell ref="A311:A316"/>
-    <mergeCell ref="F312:F313"/>
-    <mergeCell ref="G312:G313"/>
-    <mergeCell ref="K312:K313"/>
-    <mergeCell ref="L312:L313"/>
-    <mergeCell ref="M312:M313"/>
-    <mergeCell ref="N312:N313"/>
-    <mergeCell ref="G310:G311"/>
-    <mergeCell ref="K310:K311"/>
-    <mergeCell ref="L310:L311"/>
-    <mergeCell ref="M310:M311"/>
-    <mergeCell ref="N310:N311"/>
-    <mergeCell ref="O310:O311"/>
-    <mergeCell ref="Q310:Q311"/>
-    <mergeCell ref="Q312:Q313"/>
-    <mergeCell ref="O312:O313"/>
-    <mergeCell ref="P312:P313"/>
-    <mergeCell ref="U312:U313"/>
-    <mergeCell ref="T312:T313"/>
-    <mergeCell ref="A295:A297"/>
-    <mergeCell ref="A298:A300"/>
-    <mergeCell ref="A301:A302"/>
-    <mergeCell ref="A303:A304"/>
-    <mergeCell ref="A305:A308"/>
-    <mergeCell ref="F310:F311"/>
-    <mergeCell ref="A261:A265"/>
-    <mergeCell ref="A267:A270"/>
-    <mergeCell ref="A272:A276"/>
-    <mergeCell ref="A281:A282"/>
-    <mergeCell ref="A283:A284"/>
-    <mergeCell ref="A285:A293"/>
-    <mergeCell ref="E310:E311"/>
-    <mergeCell ref="A214:A218"/>
-    <mergeCell ref="A223:A228"/>
-    <mergeCell ref="A235:A240"/>
-    <mergeCell ref="A241:A247"/>
-    <mergeCell ref="A249:A251"/>
-    <mergeCell ref="A255:A260"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="A197:A200"/>
-    <mergeCell ref="A204:A206"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A169:A173"/>
-    <mergeCell ref="A174:A180"/>
-    <mergeCell ref="A183:A185"/>
-    <mergeCell ref="A187:A189"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A121:A124"/>
-    <mergeCell ref="A133:A136"/>
-    <mergeCell ref="A138:A144"/>
-    <mergeCell ref="A145:A147"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="A153:A164"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="A78:A117"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A41:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="M91:M101"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="Q91:Q92"/>
-    <mergeCell ref="T91:T92"/>
-    <mergeCell ref="E475:E476"/>
-    <mergeCell ref="U91:U92"/>
-    <mergeCell ref="M475:M476"/>
-    <mergeCell ref="K475:K476"/>
-    <mergeCell ref="L475:L476"/>
-    <mergeCell ref="U475:U476"/>
-    <mergeCell ref="U434:U435"/>
-    <mergeCell ref="H310:H311"/>
-    <mergeCell ref="H312:H313"/>
-    <mergeCell ref="J310:J311"/>
-    <mergeCell ref="I310:I311"/>
-    <mergeCell ref="I312:I313"/>
-    <mergeCell ref="J312:J313"/>
-    <mergeCell ref="E312:E313"/>
-    <mergeCell ref="K91:K101"/>
-    <mergeCell ref="L91:L101"/>
+    <mergeCell ref="A408:A411"/>
+    <mergeCell ref="A412:A416"/>
+    <mergeCell ref="A417:A424"/>
+    <mergeCell ref="A427:A433"/>
+    <mergeCell ref="A434:A439"/>
+    <mergeCell ref="K434:K435"/>
+    <mergeCell ref="T434:T435"/>
+    <mergeCell ref="L434:L435"/>
+    <mergeCell ref="M434:M435"/>
+    <mergeCell ref="N434:N435"/>
+    <mergeCell ref="O434:O435"/>
+    <mergeCell ref="P434:P435"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="14" scale="19" orientation="landscape" r:id="rId1"/>
@@ -32570,6 +32575,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010086D90174D47A804391C4DA452EC9730D" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="11305cf558cbbb68e97719bf6ef90d42">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c96d3992-be07-45a7-867c-b27a695f80ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cdbccf51d1e4c105d105367bb80d227d" ns3:_="">
     <xsd:import namespace="c96d3992-be07-45a7-867c-b27a695f80ce"/>
@@ -32725,24 +32747,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c96d3992-be07-45a7-867c-b27a695f80ce" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228C0667-8F71-40C6-9A98-A1E447AB0793}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32758,22 +32781,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA926989-63FF-4C05-9608-95BD8CEA9583}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c96d3992-be07-45a7-867c-b27a695f80ce"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683C3745-F86F-4FA4-9EFA-9CFDB6D099D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>